--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -2124,10 +2124,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122823668</v>
+        <v>122826113</v>
       </c>
       <c r="B14" t="n">
-        <v>78762</v>
+        <v>79872</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2136,25 +2136,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529038</v>
+        <v>529119</v>
       </c>
       <c r="R14" t="n">
-        <v>6998333</v>
+        <v>6998208</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122826113</v>
+        <v>122823668</v>
       </c>
       <c r="B16" t="n">
-        <v>79872</v>
+        <v>78762</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2390,25 +2390,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2418,10 +2418,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529119</v>
+        <v>529038</v>
       </c>
       <c r="R16" t="n">
-        <v>6998208</v>
+        <v>6998333</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2472,12 +2472,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122824790</v>
+        <v>122826075</v>
       </c>
       <c r="B22" t="n">
-        <v>78762</v>
+        <v>74847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3151,25 +3151,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3179,13 +3179,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528970</v>
+        <v>529120</v>
       </c>
       <c r="R22" t="n">
-        <v>6998415</v>
+        <v>6998243</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3212,11 +3212,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På ved på gammal grov björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3225,51 +3240,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122826075</v>
+        <v>122824790</v>
       </c>
       <c r="B23" t="n">
-        <v>74847</v>
+        <v>78762</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3278,25 +3268,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3306,13 +3296,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529120</v>
+        <v>528970</v>
       </c>
       <c r="R23" t="n">
-        <v>6998243</v>
+        <v>6998415</v>
       </c>
       <c r="S23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3339,26 +3329,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På ved på gammal grov björkhögstubbe</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3367,16 +3342,41 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3987,10 +3987,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122825635</v>
+        <v>122824605</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>79843</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4003,27 +4003,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4032,13 +4032,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529077</v>
+        <v>528996</v>
       </c>
       <c r="R29" t="n">
-        <v>6998245</v>
+        <v>6998338</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4070,11 +4070,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4083,6 +4078,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4099,7 +4119,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122825497</v>
+        <v>122824434</v>
       </c>
       <c r="B30" t="n">
         <v>79843</v>
@@ -4133,16 +4153,21 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529024</v>
+        <v>529000</v>
       </c>
       <c r="R30" t="n">
-        <v>6998262</v>
+        <v>6998335</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4177,6 +4202,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4185,6 +4215,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4201,10 +4256,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122824605</v>
+        <v>122825731</v>
       </c>
       <c r="B31" t="n">
-        <v>79843</v>
+        <v>78762</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4217,27 +4272,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4246,13 +4305,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528996</v>
+        <v>529058</v>
       </c>
       <c r="R31" t="n">
-        <v>6998338</v>
+        <v>6998331</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4279,11 +4338,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4292,51 +4366,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122824434</v>
+        <v>122825635</v>
       </c>
       <c r="B32" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4349,27 +4398,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4378,10 +4427,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529000</v>
+        <v>529077</v>
       </c>
       <c r="R32" t="n">
-        <v>6998335</v>
+        <v>6998245</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4418,7 +4467,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4429,31 +4478,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4470,10 +4494,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122825731</v>
+        <v>122825497</v>
       </c>
       <c r="B33" t="n">
-        <v>78762</v>
+        <v>79843</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4486,43 +4510,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529058</v>
+        <v>529024</v>
       </c>
       <c r="R33" t="n">
-        <v>6998331</v>
+        <v>6998262</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4552,24 +4567,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4584,12 +4584,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4932,7 +4932,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122826095</v>
+        <v>122825922</v>
       </c>
       <c r="B37" t="n">
         <v>79843</v>
@@ -4972,13 +4972,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529130</v>
+        <v>529093</v>
       </c>
       <c r="R37" t="n">
-        <v>6998225</v>
+        <v>6998269</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5037,22 +5037,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122825922</v>
+        <v>122825840</v>
       </c>
       <c r="B38" t="n">
-        <v>79843</v>
+        <v>79871</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5061,25 +5061,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5089,13 +5089,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529093</v>
+        <v>529095</v>
       </c>
       <c r="R38" t="n">
-        <v>6998269</v>
+        <v>6998278</v>
       </c>
       <c r="S38" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På klippa i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5166,10 +5166,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122825840</v>
+        <v>122825588</v>
       </c>
       <c r="B39" t="n">
-        <v>79871</v>
+        <v>78762</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5178,25 +5178,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5206,10 +5206,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529095</v>
+        <v>529032</v>
       </c>
       <c r="R39" t="n">
-        <v>6998278</v>
+        <v>6998357</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På klippa i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5283,10 +5283,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122825588</v>
+        <v>122826095</v>
       </c>
       <c r="B40" t="n">
-        <v>78762</v>
+        <v>79843</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5299,21 +5299,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5323,13 +5323,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529032</v>
+        <v>529130</v>
       </c>
       <c r="R40" t="n">
-        <v>6998357</v>
+        <v>6998225</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5388,12 +5388,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122825438</v>
+        <v>122825441</v>
       </c>
       <c r="B2" t="n">
-        <v>78499</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529040</v>
+        <v>529026</v>
       </c>
       <c r="R2" t="n">
-        <v>6998249</v>
+        <v>6998251</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +753,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122825991</v>
+        <v>122825664</v>
       </c>
       <c r="B3" t="n">
-        <v>79843</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529105</v>
+        <v>529058</v>
       </c>
       <c r="R3" t="n">
-        <v>6998247</v>
+        <v>6998341</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122824740</v>
+        <v>122826112</v>
       </c>
       <c r="B4" t="n">
-        <v>78762</v>
+        <v>79145</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>257107</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528995</v>
+        <v>529127</v>
       </c>
       <c r="R4" t="n">
-        <v>6998368</v>
+        <v>6998223</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,14 +977,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,51 +1005,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122825432</v>
+        <v>122823668</v>
       </c>
       <c r="B5" t="n">
-        <v>78498</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529040</v>
+        <v>529038</v>
       </c>
       <c r="R5" t="n">
-        <v>6998249</v>
+        <v>6998333</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,26 +1094,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1142,26 +1107,51 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122825983</v>
+        <v>122825401</v>
       </c>
       <c r="B6" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,37 +1164,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529112</v>
+        <v>529023</v>
       </c>
       <c r="R6" t="n">
-        <v>6998258</v>
+        <v>6998251</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1238,7 +1233,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,31 +1244,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1290,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122825531</v>
+        <v>122825504</v>
       </c>
       <c r="B7" t="n">
-        <v>79872</v>
+        <v>79875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,42 +1276,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529096</v>
+        <v>529093</v>
       </c>
       <c r="R7" t="n">
-        <v>6998283</v>
+        <v>6998292</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1412,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122826028</v>
+        <v>122824740</v>
       </c>
       <c r="B8" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1452,13 +1417,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529125</v>
+        <v>528995</v>
       </c>
       <c r="R8" t="n">
-        <v>6998223</v>
+        <v>6998368</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1490,6 +1455,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1506,22 +1476,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1539,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122823485</v>
+        <v>122825922</v>
       </c>
       <c r="B9" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1555,42 +1525,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529041</v>
+        <v>529093</v>
       </c>
       <c r="R9" t="n">
-        <v>6998374</v>
+        <v>6998269</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1617,14 +1582,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,51 +1610,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122825664</v>
+        <v>122826095</v>
       </c>
       <c r="B10" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1692,21 +1642,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1716,13 +1666,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529058</v>
+        <v>529130</v>
       </c>
       <c r="R10" t="n">
-        <v>6998341</v>
+        <v>6998225</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1751,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1761,12 +1711,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1781,22 +1731,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122825781</v>
+        <v>122823649</v>
       </c>
       <c r="B11" t="n">
-        <v>95893</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1809,37 +1759,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529100</v>
+        <v>529030</v>
       </c>
       <c r="R11" t="n">
-        <v>6998226</v>
+        <v>6998340</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1871,6 +1826,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långväxta fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1879,6 +1839,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1895,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122825504</v>
+        <v>122825738</v>
       </c>
       <c r="B12" t="n">
-        <v>79871</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1907,41 +1892,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529093</v>
+        <v>529116</v>
       </c>
       <c r="R12" t="n">
-        <v>6998292</v>
+        <v>6998284</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1968,11 +1962,21 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1981,41 +1985,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122825467</v>
+        <v>122826435</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2028,39 +2017,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529022</v>
+        <v>529156</v>
       </c>
       <c r="R13" t="n">
-        <v>6998263</v>
+        <v>6998208</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2093,11 +2077,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2124,10 +2103,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122826113</v>
+        <v>122826075</v>
       </c>
       <c r="B14" t="n">
-        <v>79872</v>
+        <v>74847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2140,21 +2119,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2164,13 +2143,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529119</v>
+        <v>529120</v>
       </c>
       <c r="R14" t="n">
-        <v>6998208</v>
+        <v>6998243</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2197,11 +2176,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På ved på gammal grov björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2210,51 +2204,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122823879</v>
+        <v>122825840</v>
       </c>
       <c r="B15" t="n">
-        <v>78762</v>
+        <v>79875</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2263,25 +2232,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2291,13 +2260,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529056</v>
+        <v>529095</v>
       </c>
       <c r="R15" t="n">
-        <v>6998335</v>
+        <v>6998278</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2324,11 +2293,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På klippa i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2337,51 +2321,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122823668</v>
+        <v>122824434</v>
       </c>
       <c r="B16" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2394,34 +2353,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529038</v>
+        <v>529000</v>
       </c>
       <c r="R16" t="n">
-        <v>6998333</v>
+        <v>6998335</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2456,6 +2420,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2472,12 +2441,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -2487,7 +2456,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2505,10 +2474,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122825395</v>
+        <v>122825546</v>
       </c>
       <c r="B17" t="n">
-        <v>78762</v>
+        <v>79751</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2517,25 +2486,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2545,10 +2514,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529085</v>
+        <v>529031</v>
       </c>
       <c r="R17" t="n">
-        <v>6998292</v>
+        <v>6998345</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2578,11 +2547,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2591,51 +2575,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122823202</v>
+        <v>122825639</v>
       </c>
       <c r="B18" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2672,13 +2631,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529003</v>
+        <v>529113</v>
       </c>
       <c r="R18" t="n">
-        <v>6998380</v>
+        <v>6998294</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2721,27 +2680,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2759,10 +2718,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122826112</v>
+        <v>122824605</v>
       </c>
       <c r="B19" t="n">
-        <v>79141</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2775,37 +2734,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>257107</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529127</v>
+        <v>528996</v>
       </c>
       <c r="R19" t="n">
-        <v>6998223</v>
+        <v>6998338</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2832,26 +2796,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2860,26 +2809,51 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122825738</v>
+        <v>122825781</v>
       </c>
       <c r="B20" t="n">
-        <v>78762</v>
+        <v>95901</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2892,46 +2866,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529116</v>
+        <v>529100</v>
       </c>
       <c r="R20" t="n">
-        <v>6998284</v>
+        <v>6998226</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2958,19 +2923,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2985,22 +2940,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122824230</v>
+        <v>122826028</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3013,47 +2968,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529044</v>
+        <v>529125</v>
       </c>
       <c r="R21" t="n">
-        <v>6998360</v>
+        <v>6998223</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3085,11 +3030,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3101,27 +3041,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3139,10 +3079,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122826075</v>
+        <v>122825731</v>
       </c>
       <c r="B22" t="n">
-        <v>74847</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3151,41 +3091,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529120</v>
+        <v>529058</v>
       </c>
       <c r="R22" t="n">
-        <v>6998243</v>
+        <v>6998331</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3214,7 +3163,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3224,12 +3173,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På ved på gammal grov björkhögstubbe</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3256,10 +3205,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122824790</v>
+        <v>122824569</v>
       </c>
       <c r="B23" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3272,21 +3221,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3296,13 +3245,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528970</v>
+        <v>528994</v>
       </c>
       <c r="R23" t="n">
-        <v>6998415</v>
+        <v>6998342</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3334,6 +3283,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Lunglav på gran intill en asp med lunglav.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3350,22 +3304,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3383,10 +3337,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122825546</v>
+        <v>122825991</v>
       </c>
       <c r="B24" t="n">
-        <v>79747</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3395,25 +3349,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3423,10 +3377,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529031</v>
+        <v>529105</v>
       </c>
       <c r="R24" t="n">
-        <v>6998345</v>
+        <v>6998247</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3458,7 +3412,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3468,7 +3422,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3500,10 +3454,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122826435</v>
+        <v>122824230</v>
       </c>
       <c r="B25" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3516,37 +3470,47 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529156</v>
+        <v>529044</v>
       </c>
       <c r="R25" t="n">
-        <v>6998208</v>
+        <v>6998360</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3578,6 +3542,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3586,6 +3555,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3602,10 +3596,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122825639</v>
+        <v>122823879</v>
       </c>
       <c r="B26" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3642,13 +3636,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529113</v>
+        <v>529056</v>
       </c>
       <c r="R26" t="n">
-        <v>6998294</v>
+        <v>6998335</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3691,27 +3685,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3729,10 +3723,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122824569</v>
+        <v>122826113</v>
       </c>
       <c r="B27" t="n">
-        <v>79843</v>
+        <v>79876</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3741,25 +3735,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3769,13 +3763,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528994</v>
+        <v>529119</v>
       </c>
       <c r="R27" t="n">
-        <v>6998342</v>
+        <v>6998208</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3807,11 +3801,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Lunglav på gran intill en asp med lunglav.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3828,22 +3817,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3864,7 +3853,7 @@
         <v>122826011</v>
       </c>
       <c r="B28" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3987,10 +3976,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122824605</v>
+        <v>122825531</v>
       </c>
       <c r="B29" t="n">
-        <v>79843</v>
+        <v>79876</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3999,31 +3988,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4032,13 +4021,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528996</v>
+        <v>529096</v>
       </c>
       <c r="R29" t="n">
-        <v>6998338</v>
+        <v>6998283</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4084,24 +4073,14 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4119,10 +4098,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122824434</v>
+        <v>122825588</v>
       </c>
       <c r="B30" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4135,39 +4114,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529000</v>
+        <v>529032</v>
       </c>
       <c r="R30" t="n">
-        <v>6998335</v>
+        <v>6998357</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4197,14 +4171,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4215,51 +4199,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122825731</v>
+        <v>122825467</v>
       </c>
       <c r="B31" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4272,31 +4231,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4305,10 +4260,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529058</v>
+        <v>529022</v>
       </c>
       <c r="R31" t="n">
-        <v>6998331</v>
+        <v>6998263</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4338,24 +4293,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4370,19 +4315,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122825635</v>
+        <v>122825875</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4427,10 +4372,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529077</v>
+        <v>529132</v>
       </c>
       <c r="R32" t="n">
-        <v>6998245</v>
+        <v>6998196</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4467,7 +4412,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4494,10 +4439,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122825497</v>
+        <v>122825635</v>
       </c>
       <c r="B33" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4510,34 +4455,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529024</v>
+        <v>529077</v>
       </c>
       <c r="R33" t="n">
-        <v>6998262</v>
+        <v>6998245</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4570,6 +4520,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4596,10 +4551,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122825401</v>
+        <v>122823202</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4612,39 +4567,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529023</v>
+        <v>529003</v>
       </c>
       <c r="R34" t="n">
-        <v>6998251</v>
+        <v>6998380</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4679,11 +4629,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4692,6 +4637,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4708,10 +4678,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122825441</v>
+        <v>122825395</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4724,39 +4694,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529026</v>
+        <v>529085</v>
       </c>
       <c r="R35" t="n">
-        <v>6998251</v>
+        <v>6998292</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4791,11 +4756,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4804,6 +4764,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4820,10 +4805,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122825875</v>
+        <v>122825983</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4836,42 +4821,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529132</v>
+        <v>529112</v>
       </c>
       <c r="R36" t="n">
-        <v>6998196</v>
+        <v>6998258</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4905,7 +4885,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4916,6 +4896,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4932,10 +4937,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122825922</v>
+        <v>122825497</v>
       </c>
       <c r="B37" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4972,13 +4977,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529093</v>
+        <v>529024</v>
       </c>
       <c r="R37" t="n">
-        <v>6998269</v>
+        <v>6998262</v>
       </c>
       <c r="S37" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5005,24 +5010,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5037,22 +5027,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122825840</v>
+        <v>122824790</v>
       </c>
       <c r="B38" t="n">
-        <v>79871</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5061,25 +5051,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5089,10 +5079,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529095</v>
+        <v>528970</v>
       </c>
       <c r="R38" t="n">
-        <v>6998278</v>
+        <v>6998415</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5122,26 +5112,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På klippa i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5150,26 +5125,51 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122825588</v>
+        <v>122825432</v>
       </c>
       <c r="B39" t="n">
-        <v>78762</v>
+        <v>78502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5182,21 +5182,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5206,10 +5206,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529032</v>
+        <v>529040</v>
       </c>
       <c r="R39" t="n">
-        <v>6998357</v>
+        <v>6998249</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5283,10 +5283,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122826095</v>
+        <v>122823485</v>
       </c>
       <c r="B40" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5299,34 +5299,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529130</v>
+        <v>529041</v>
       </c>
       <c r="R40" t="n">
-        <v>6998225</v>
+        <v>6998374</v>
       </c>
       <c r="S40" t="n">
         <v>8</v>
@@ -5356,24 +5361,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5384,26 +5379,51 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122823649</v>
+        <v>122825438</v>
       </c>
       <c r="B41" t="n">
-        <v>78762</v>
+        <v>78503</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5416,42 +5436,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529030</v>
+        <v>529040</v>
       </c>
       <c r="R41" t="n">
-        <v>6998340</v>
+        <v>6998249</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5478,14 +5493,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar.</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5496,41 +5521,16 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122825441</v>
+        <v>122825664</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529026</v>
+        <v>529058</v>
       </c>
       <c r="R2" t="n">
-        <v>6998251</v>
+        <v>6998341</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,14 +748,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122825664</v>
+        <v>122825441</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529058</v>
+        <v>529026</v>
       </c>
       <c r="R3" t="n">
-        <v>6998341</v>
+        <v>6998251</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,24 +870,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,12 +892,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122824605</v>
+        <v>122825781</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>95901</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2734,42 +2734,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528996</v>
+        <v>529100</v>
       </c>
       <c r="R19" t="n">
-        <v>6998338</v>
+        <v>6998226</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2809,31 +2804,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2850,10 +2820,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122825781</v>
+        <v>122824605</v>
       </c>
       <c r="B20" t="n">
-        <v>95901</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2866,37 +2836,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529100</v>
+        <v>528996</v>
       </c>
       <c r="R20" t="n">
-        <v>6998226</v>
+        <v>6998338</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2936,6 +2911,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -4098,10 +4098,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122825588</v>
+        <v>122825467</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4114,34 +4114,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529032</v>
+        <v>529022</v>
       </c>
       <c r="R30" t="n">
-        <v>6998357</v>
+        <v>6998263</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4171,24 +4176,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4203,22 +4198,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122825467</v>
+        <v>122825588</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4231,39 +4226,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529022</v>
+        <v>529032</v>
       </c>
       <c r="R31" t="n">
-        <v>6998263</v>
+        <v>6998357</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4293,14 +4283,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4315,12 +4315,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122825664</v>
+        <v>122825731</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,24 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
@@ -718,7 +727,7 @@
         <v>529058</v>
       </c>
       <c r="R2" t="n">
-        <v>6998341</v>
+        <v>6998331</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122825441</v>
+        <v>122825432</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>78502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +817,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529026</v>
+        <v>529040</v>
       </c>
       <c r="R3" t="n">
-        <v>6998251</v>
+        <v>6998249</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,14 +874,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +906,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122826112</v>
+        <v>122825991</v>
       </c>
       <c r="B4" t="n">
-        <v>79145</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>257107</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529127</v>
+        <v>529105</v>
       </c>
       <c r="R4" t="n">
-        <v>6998223</v>
+        <v>6998247</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1021,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122823668</v>
+        <v>122825983</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1061,13 +1075,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529038</v>
+        <v>529112</v>
       </c>
       <c r="R5" t="n">
-        <v>6998333</v>
+        <v>6998258</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,6 +1113,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1115,12 +1134,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1130,7 +1149,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1148,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122825401</v>
+        <v>122823668</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,39 +1183,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529023</v>
+        <v>529038</v>
       </c>
       <c r="R6" t="n">
-        <v>6998251</v>
+        <v>6998333</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,11 +1245,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1244,6 +1253,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1260,10 +1294,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122825504</v>
+        <v>122825441</v>
       </c>
       <c r="B7" t="n">
-        <v>79875</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,38 +1306,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529093</v>
+        <v>529026</v>
       </c>
       <c r="R7" t="n">
-        <v>6998292</v>
+        <v>6998251</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,6 +1377,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1346,21 +1390,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1377,10 +1406,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122824740</v>
+        <v>122825546</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,25 +1418,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1446,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528995</v>
+        <v>529031</v>
       </c>
       <c r="R8" t="n">
-        <v>6998368</v>
+        <v>6998345</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,14 +1479,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,48 +1507,23 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122825922</v>
+        <v>122826095</v>
       </c>
       <c r="B9" t="n">
         <v>79847</v>
@@ -1549,13 +1563,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529093</v>
+        <v>529130</v>
       </c>
       <c r="R9" t="n">
-        <v>6998269</v>
+        <v>6998225</v>
       </c>
       <c r="S9" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1584,7 +1598,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,12 +1608,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,22 +1628,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122826095</v>
+        <v>122825635</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1642,37 +1656,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529130</v>
+        <v>529077</v>
       </c>
       <c r="R10" t="n">
-        <v>6998225</v>
+        <v>6998245</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1699,24 +1718,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,22 +1740,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122823649</v>
+        <v>122825467</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,27 +1768,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1788,13 +1797,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529030</v>
+        <v>529022</v>
       </c>
       <c r="R11" t="n">
-        <v>6998340</v>
+        <v>6998263</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1828,7 +1837,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,31 +1848,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1880,10 +1864,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122825738</v>
+        <v>122825438</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1896,46 +1880,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529116</v>
+        <v>529040</v>
       </c>
       <c r="R12" t="n">
-        <v>6998284</v>
+        <v>6998249</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1964,7 +1939,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1974,7 +1949,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1989,22 +1969,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122826435</v>
+        <v>122826075</v>
       </c>
       <c r="B13" t="n">
-        <v>90944</v>
+        <v>74847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,25 +1993,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2041,13 +2021,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529156</v>
+        <v>529120</v>
       </c>
       <c r="R13" t="n">
-        <v>6998208</v>
+        <v>6998243</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2074,9 +2054,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På ved på gammal grov björkhögstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,22 +2086,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122826075</v>
+        <v>122823202</v>
       </c>
       <c r="B14" t="n">
-        <v>74847</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2115,25 +2110,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2143,13 +2138,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529120</v>
+        <v>529003</v>
       </c>
       <c r="R14" t="n">
-        <v>6998243</v>
+        <v>6998380</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2176,26 +2171,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På ved på gammal grov björkhögstubbe</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2204,26 +2184,51 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122825840</v>
+        <v>122825738</v>
       </c>
       <c r="B15" t="n">
-        <v>79875</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2232,41 +2237,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529095</v>
+        <v>529116</v>
       </c>
       <c r="R15" t="n">
-        <v>6998278</v>
+        <v>6998284</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2295,7 +2309,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2305,12 +2319,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På klippa i gammal barrblandskog</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2325,22 +2334,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122824434</v>
+        <v>122825401</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2353,27 +2362,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2382,10 +2391,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529000</v>
+        <v>529023</v>
       </c>
       <c r="R16" t="n">
-        <v>6998335</v>
+        <v>6998251</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2422,7 +2431,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2433,31 +2442,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2474,10 +2458,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122825546</v>
+        <v>122825875</v>
       </c>
       <c r="B17" t="n">
-        <v>79751</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2486,38 +2470,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529031</v>
+        <v>529132</v>
       </c>
       <c r="R17" t="n">
-        <v>6998345</v>
+        <v>6998196</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2547,24 +2536,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2579,19 +2558,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122825639</v>
+        <v>122825395</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2631,13 +2610,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529113</v>
+        <v>529085</v>
       </c>
       <c r="R18" t="n">
-        <v>6998294</v>
+        <v>6998292</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2685,22 +2664,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2820,7 +2799,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122824605</v>
+        <v>122824569</v>
       </c>
       <c r="B20" t="n">
         <v>79847</v>
@@ -2854,24 +2833,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528996</v>
+        <v>528994</v>
       </c>
       <c r="R20" t="n">
-        <v>6998338</v>
+        <v>6998342</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2903,6 +2877,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Lunglav på gran intill en asp med lunglav.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2919,22 +2898,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2952,10 +2931,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122826028</v>
+        <v>122825639</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2968,21 +2947,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2992,10 +2971,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529125</v>
+        <v>529113</v>
       </c>
       <c r="R21" t="n">
-        <v>6998223</v>
+        <v>6998294</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -3046,12 +3025,12 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -3061,7 +3040,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3079,7 +3058,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122825731</v>
+        <v>122824740</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -3112,26 +3091,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529058</v>
+        <v>528995</v>
       </c>
       <c r="R22" t="n">
-        <v>6998331</v>
+        <v>6998368</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3161,24 +3131,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3189,26 +3149,51 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122824569</v>
+        <v>122825664</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3221,21 +3206,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3245,13 +3230,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528994</v>
+        <v>529058</v>
       </c>
       <c r="R23" t="n">
-        <v>6998342</v>
+        <v>6998341</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3278,14 +3263,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Lunglav på gran intill en asp med lunglav.</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3296,48 +3291,23 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122825991</v>
+        <v>122826011</v>
       </c>
       <c r="B24" t="n">
         <v>79847</v>
@@ -3370,20 +3340,29 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529105</v>
+        <v>529111</v>
       </c>
       <c r="R24" t="n">
-        <v>6998247</v>
+        <v>6998222</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3412,7 +3391,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3422,12 +3401,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3442,22 +3421,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122824230</v>
+        <v>122825840</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>79875</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3466,51 +3445,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529044</v>
+        <v>529095</v>
       </c>
       <c r="R25" t="n">
-        <v>6998360</v>
+        <v>6998278</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3537,14 +3506,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
+          <t>På klippa i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3555,51 +3534,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122823879</v>
+        <v>122826028</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3612,21 +3566,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3636,13 +3590,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529056</v>
+        <v>529125</v>
       </c>
       <c r="R26" t="n">
-        <v>6998335</v>
+        <v>6998223</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3685,27 +3639,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3723,10 +3677,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122826113</v>
+        <v>122825504</v>
       </c>
       <c r="B27" t="n">
-        <v>79876</v>
+        <v>79875</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3739,21 +3693,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3763,10 +3717,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529119</v>
+        <v>529093</v>
       </c>
       <c r="R27" t="n">
-        <v>6998208</v>
+        <v>6998292</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3815,24 +3769,14 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3850,10 +3794,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122826011</v>
+        <v>122823649</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3866,31 +3810,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3899,13 +3839,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529111</v>
+        <v>529030</v>
       </c>
       <c r="R28" t="n">
-        <v>6998222</v>
+        <v>6998340</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3932,24 +3872,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>Långväxta fertila bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3960,26 +3890,51 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122825531</v>
+        <v>122824230</v>
       </c>
       <c r="B29" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3988,31 +3943,36 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4021,13 +3981,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529096</v>
+        <v>529044</v>
       </c>
       <c r="R29" t="n">
-        <v>6998283</v>
+        <v>6998360</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4059,6 +4019,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4070,17 +4035,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Sten/berg på land</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stone/rock on land</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4098,10 +4073,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122825467</v>
+        <v>122826435</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4114,39 +4089,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529022</v>
+        <v>529156</v>
       </c>
       <c r="R30" t="n">
-        <v>6998263</v>
+        <v>6998208</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4179,11 +4149,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4210,7 +4175,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122825588</v>
+        <v>122823485</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -4244,19 +4209,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529032</v>
+        <v>529041</v>
       </c>
       <c r="R31" t="n">
-        <v>6998357</v>
+        <v>6998374</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4283,24 +4253,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4311,26 +4271,51 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122825875</v>
+        <v>122825588</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4343,39 +4328,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529132</v>
+        <v>529032</v>
       </c>
       <c r="R32" t="n">
-        <v>6998196</v>
+        <v>6998357</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4405,14 +4385,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4427,22 +4417,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122825635</v>
+        <v>122823879</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4455,42 +4445,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529077</v>
+        <v>529056</v>
       </c>
       <c r="R33" t="n">
-        <v>6998245</v>
+        <v>6998335</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4522,11 +4507,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4535,6 +4515,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4551,10 +4556,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122823202</v>
+        <v>122824434</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4567,34 +4572,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529003</v>
+        <v>529000</v>
       </c>
       <c r="R34" t="n">
-        <v>6998380</v>
+        <v>6998335</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4629,6 +4639,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4640,27 +4655,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4678,10 +4693,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122825395</v>
+        <v>122825531</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4690,41 +4705,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529085</v>
+        <v>529096</v>
       </c>
       <c r="R35" t="n">
-        <v>6998292</v>
+        <v>6998283</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4770,24 +4790,14 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4805,10 +4815,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122825983</v>
+        <v>122826112</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>79145</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4821,21 +4831,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>257107</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4845,13 +4855,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529112</v>
+        <v>529127</v>
       </c>
       <c r="R36" t="n">
-        <v>6998258</v>
+        <v>6998223</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4878,14 +4888,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4896,51 +4916,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122825497</v>
+        <v>122824790</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4953,21 +4948,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4977,10 +4972,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529024</v>
+        <v>528970</v>
       </c>
       <c r="R37" t="n">
-        <v>6998262</v>
+        <v>6998415</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5023,6 +5018,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5039,10 +5059,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122824790</v>
+        <v>122826113</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5051,25 +5071,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5079,10 +5099,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528970</v>
+        <v>529119</v>
       </c>
       <c r="R38" t="n">
-        <v>6998415</v>
+        <v>6998208</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5133,12 +5153,12 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -5148,7 +5168,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5166,10 +5186,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122825432</v>
+        <v>122825497</v>
       </c>
       <c r="B39" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5182,21 +5202,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5206,10 +5226,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529040</v>
+        <v>529024</v>
       </c>
       <c r="R39" t="n">
-        <v>6998249</v>
+        <v>6998262</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5239,24 +5259,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5271,22 +5276,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122823485</v>
+        <v>122824605</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5299,27 +5304,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5328,13 +5333,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529041</v>
+        <v>528996</v>
       </c>
       <c r="R40" t="n">
-        <v>6998374</v>
+        <v>6998338</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5366,11 +5371,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5382,27 +5382,27 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5420,10 +5420,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122825438</v>
+        <v>122825922</v>
       </c>
       <c r="B41" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5436,21 +5436,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5460,13 +5460,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529040</v>
+        <v>529093</v>
       </c>
       <c r="R41" t="n">
-        <v>6998249</v>
+        <v>6998269</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122825731</v>
+        <v>122824230</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529058</v>
+        <v>529044</v>
       </c>
       <c r="R2" t="n">
-        <v>6998331</v>
+        <v>6998360</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,24 +758,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,26 +776,51 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122825432</v>
+        <v>122825438</v>
       </c>
       <c r="B3" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +833,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -918,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122825991</v>
+        <v>122825467</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,34 +950,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529105</v>
+        <v>529022</v>
       </c>
       <c r="R4" t="n">
-        <v>6998247</v>
+        <v>6998263</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,24 +1012,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,22 +1034,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122825983</v>
+        <v>122826435</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,21 +1062,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1075,13 +1086,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529112</v>
+        <v>529156</v>
       </c>
       <c r="R5" t="n">
-        <v>6998258</v>
+        <v>6998208</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,11 +1124,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1126,31 +1132,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1167,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122823668</v>
+        <v>122825922</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,21 +1164,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1207,13 +1188,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529038</v>
+        <v>529093</v>
       </c>
       <c r="R6" t="n">
-        <v>6998333</v>
+        <v>6998269</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,11 +1221,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1253,48 +1249,23 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122825441</v>
+        <v>122825875</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1339,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529026</v>
+        <v>529132</v>
       </c>
       <c r="R7" t="n">
-        <v>6998251</v>
+        <v>6998196</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1379,7 +1350,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122825546</v>
+        <v>122825635</v>
       </c>
       <c r="B8" t="n">
-        <v>79751</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,38 +1389,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529031</v>
+        <v>529077</v>
       </c>
       <c r="R8" t="n">
-        <v>6998345</v>
+        <v>6998245</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,24 +1455,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,19 +1477,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122826095</v>
+        <v>122824605</v>
       </c>
       <c r="B9" t="n">
         <v>79847</v>
@@ -1557,19 +1523,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529130</v>
+        <v>528996</v>
       </c>
       <c r="R9" t="n">
-        <v>6998225</v>
+        <v>6998338</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1596,26 +1567,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1624,26 +1580,51 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122825635</v>
+        <v>122826011</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1656,27 +1637,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1685,13 +1670,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529077</v>
+        <v>529111</v>
       </c>
       <c r="R10" t="n">
-        <v>6998245</v>
+        <v>6998222</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1718,14 +1703,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,22 +1735,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122825467</v>
+        <v>122825991</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1768,39 +1763,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529022</v>
+        <v>529105</v>
       </c>
       <c r="R11" t="n">
-        <v>6998263</v>
+        <v>6998247</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1830,14 +1820,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,22 +1852,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122825438</v>
+        <v>122826028</v>
       </c>
       <c r="B12" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,21 +1880,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529040</v>
+        <v>529125</v>
       </c>
       <c r="R12" t="n">
-        <v>6998249</v>
+        <v>6998223</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1937,26 +1937,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1965,26 +1950,51 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122826075</v>
+        <v>122826095</v>
       </c>
       <c r="B13" t="n">
-        <v>74847</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1993,25 +2003,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2021,13 +2031,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529120</v>
+        <v>529130</v>
       </c>
       <c r="R13" t="n">
-        <v>6998243</v>
+        <v>6998225</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2056,7 +2066,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2066,12 +2076,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På ved på gammal grov björkhögstubbe</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,19 +2096,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122823202</v>
+        <v>122825395</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -2138,10 +2148,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529003</v>
+        <v>529085</v>
       </c>
       <c r="R14" t="n">
-        <v>6998380</v>
+        <v>6998292</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2187,7 +2197,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2225,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122825738</v>
+        <v>122825432</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2241,46 +2251,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529116</v>
+        <v>529040</v>
       </c>
       <c r="R15" t="n">
-        <v>6998284</v>
+        <v>6998249</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2309,7 +2310,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2319,7 +2320,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2334,22 +2340,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122825401</v>
+        <v>122823649</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2362,27 +2368,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2391,13 +2397,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529023</v>
+        <v>529030</v>
       </c>
       <c r="R16" t="n">
-        <v>6998251</v>
+        <v>6998340</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2431,7 +2437,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Långväxta fertila bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2442,6 +2448,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2458,10 +2489,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122825875</v>
+        <v>122823879</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2474,42 +2505,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529132</v>
+        <v>529056</v>
       </c>
       <c r="R17" t="n">
-        <v>6998196</v>
+        <v>6998335</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2541,11 +2567,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2554,6 +2575,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2570,10 +2616,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122825395</v>
+        <v>122826075</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>74847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2582,25 +2628,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2610,13 +2656,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529085</v>
+        <v>529120</v>
       </c>
       <c r="R18" t="n">
-        <v>6998292</v>
+        <v>6998243</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2643,11 +2689,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På ved på gammal grov björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2656,51 +2717,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122825781</v>
+        <v>122824790</v>
       </c>
       <c r="B19" t="n">
-        <v>95901</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2713,21 +2749,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2737,10 +2773,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529100</v>
+        <v>528970</v>
       </c>
       <c r="R19" t="n">
-        <v>6998226</v>
+        <v>6998415</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2783,6 +2819,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2799,10 +2860,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122824569</v>
+        <v>122823668</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2815,21 +2876,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2839,13 +2900,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528994</v>
+        <v>529038</v>
       </c>
       <c r="R20" t="n">
-        <v>6998342</v>
+        <v>6998333</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2877,11 +2938,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Lunglav på gran intill en asp med lunglav.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2898,22 +2954,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2931,10 +2987,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122825639</v>
+        <v>122825504</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>79875</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2943,25 +2999,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2971,13 +3027,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529113</v>
+        <v>529093</v>
       </c>
       <c r="R21" t="n">
-        <v>6998294</v>
+        <v>6998292</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3023,24 +3079,14 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3058,10 +3104,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122824740</v>
+        <v>122825781</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>95903</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3074,21 +3120,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3098,10 +3144,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528995</v>
+        <v>529100</v>
       </c>
       <c r="R22" t="n">
-        <v>6998368</v>
+        <v>6998226</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3136,11 +3182,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3149,31 +3190,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3190,10 +3206,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122825664</v>
+        <v>122824434</v>
       </c>
       <c r="B23" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3206,34 +3222,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529058</v>
+        <v>529000</v>
       </c>
       <c r="R23" t="n">
-        <v>6998341</v>
+        <v>6998335</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3263,24 +3284,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3291,26 +3302,51 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122826011</v>
+        <v>122825983</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3323,46 +3359,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529111</v>
+        <v>529112</v>
       </c>
       <c r="R24" t="n">
-        <v>6998222</v>
+        <v>6998258</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3389,24 +3416,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3417,26 +3434,51 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122825840</v>
+        <v>122825731</v>
       </c>
       <c r="B25" t="n">
-        <v>79875</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3445,38 +3487,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529095</v>
+        <v>529058</v>
       </c>
       <c r="R25" t="n">
-        <v>6998278</v>
+        <v>6998331</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3508,7 +3559,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3518,12 +3569,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På klippa i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3550,10 +3601,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122826028</v>
+        <v>122825639</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3566,21 +3617,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3590,10 +3641,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529125</v>
+        <v>529113</v>
       </c>
       <c r="R26" t="n">
-        <v>6998223</v>
+        <v>6998294</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -3644,12 +3695,12 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -3659,7 +3710,7 @@
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3677,10 +3728,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122825504</v>
+        <v>122825401</v>
       </c>
       <c r="B27" t="n">
-        <v>79875</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3689,38 +3740,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529093</v>
+        <v>529023</v>
       </c>
       <c r="R27" t="n">
-        <v>6998292</v>
+        <v>6998251</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3755,6 +3811,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3763,21 +3824,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3794,10 +3840,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122823649</v>
+        <v>122825664</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3810,42 +3856,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529030</v>
+        <v>529058</v>
       </c>
       <c r="R28" t="n">
-        <v>6998340</v>
+        <v>6998341</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3872,14 +3913,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar.</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3890,51 +3941,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122824230</v>
+        <v>122823202</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3947,47 +3973,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529044</v>
+        <v>529003</v>
       </c>
       <c r="R29" t="n">
-        <v>6998360</v>
+        <v>6998380</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4019,11 +4035,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4035,7 +4046,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4050,12 +4061,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4073,10 +4084,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122826435</v>
+        <v>122823485</v>
       </c>
       <c r="B30" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4089,37 +4100,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529156</v>
+        <v>529041</v>
       </c>
       <c r="R30" t="n">
-        <v>6998208</v>
+        <v>6998374</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4151,6 +4167,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4159,6 +4180,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4175,10 +4221,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122823485</v>
+        <v>122825497</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4191,42 +4237,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529041</v>
+        <v>529024</v>
       </c>
       <c r="R31" t="n">
-        <v>6998374</v>
+        <v>6998262</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4258,11 +4299,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4271,31 +4307,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4312,10 +4323,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122825588</v>
+        <v>122825531</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4324,41 +4335,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529032</v>
+        <v>529096</v>
       </c>
       <c r="R32" t="n">
-        <v>6998357</v>
+        <v>6998283</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4385,26 +4401,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4413,26 +4414,41 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122823879</v>
+        <v>122826112</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>79145</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4445,21 +4461,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>257107</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4469,13 +4485,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529056</v>
+        <v>529127</v>
       </c>
       <c r="R33" t="n">
-        <v>6998335</v>
+        <v>6998223</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4502,11 +4518,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4515,51 +4546,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122824434</v>
+        <v>122825546</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4568,43 +4574,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529000</v>
+        <v>529031</v>
       </c>
       <c r="R34" t="n">
-        <v>6998335</v>
+        <v>6998345</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4634,14 +4635,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4652,48 +4663,23 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122825531</v>
+        <v>122826113</v>
       </c>
       <c r="B35" t="n">
         <v>79876</v>
@@ -4727,24 +4713,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529096</v>
+        <v>529119</v>
       </c>
       <c r="R35" t="n">
-        <v>6998283</v>
+        <v>6998208</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4790,14 +4771,24 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Sten/berg på land</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stone/rock on land</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4815,10 +4806,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122826112</v>
+        <v>122825840</v>
       </c>
       <c r="B36" t="n">
-        <v>79145</v>
+        <v>79875</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4827,25 +4818,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>257107</v>
+        <v>6461</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4855,10 +4846,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529127</v>
+        <v>529095</v>
       </c>
       <c r="R36" t="n">
-        <v>6998223</v>
+        <v>6998278</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4890,7 +4881,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4900,12 +4891,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På klippa i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4932,10 +4923,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122824790</v>
+        <v>122824569</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4948,21 +4939,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4972,13 +4963,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528970</v>
+        <v>528994</v>
       </c>
       <c r="R37" t="n">
-        <v>6998415</v>
+        <v>6998342</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5010,6 +5001,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Lunglav på gran intill en asp med lunglav.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5026,22 +5022,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5059,10 +5055,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122826113</v>
+        <v>122825738</v>
       </c>
       <c r="B38" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5071,41 +5067,50 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529119</v>
+        <v>529116</v>
       </c>
       <c r="R38" t="n">
-        <v>6998208</v>
+        <v>6998284</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5132,11 +5137,21 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5145,51 +5160,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122825497</v>
+        <v>122825588</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5202,21 +5192,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5226,10 +5216,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529024</v>
+        <v>529032</v>
       </c>
       <c r="R39" t="n">
-        <v>6998262</v>
+        <v>6998357</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5259,9 +5249,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5276,22 +5281,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122824605</v>
+        <v>122824740</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5304,42 +5309,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528996</v>
+        <v>528995</v>
       </c>
       <c r="R40" t="n">
-        <v>6998338</v>
+        <v>6998368</v>
       </c>
       <c r="S40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5371,6 +5371,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5387,22 +5392,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5420,10 +5425,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122825922</v>
+        <v>122825441</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5436,37 +5441,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529093</v>
+        <v>529026</v>
       </c>
       <c r="R41" t="n">
-        <v>6998269</v>
+        <v>6998251</v>
       </c>
       <c r="S41" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5493,24 +5503,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5525,12 +5525,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122824230</v>
+        <v>122825438</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,47 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529044</v>
+        <v>529040</v>
       </c>
       <c r="R2" t="n">
-        <v>6998360</v>
+        <v>6998249</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,14 +748,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,51 +776,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122825438</v>
+        <v>122824230</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,37 +808,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529040</v>
+        <v>529044</v>
       </c>
       <c r="R3" t="n">
-        <v>6998249</v>
+        <v>6998360</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,24 +875,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,16 +893,41 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122826435</v>
+        <v>122825875</v>
       </c>
       <c r="B5" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,34 +1062,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529156</v>
+        <v>529132</v>
       </c>
       <c r="R5" t="n">
-        <v>6998208</v>
+        <v>6998196</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,6 +1127,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122825922</v>
+        <v>122825635</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,37 +1174,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529093</v>
+        <v>529077</v>
       </c>
       <c r="R6" t="n">
-        <v>6998269</v>
+        <v>6998245</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,24 +1236,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,22 +1258,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122825875</v>
+        <v>122826435</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,39 +1286,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529132</v>
+        <v>529156</v>
       </c>
       <c r="R7" t="n">
-        <v>6998196</v>
+        <v>6998208</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,11 +1346,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122825635</v>
+        <v>122825922</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,42 +1388,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529077</v>
+        <v>529093</v>
       </c>
       <c r="R8" t="n">
-        <v>6998245</v>
+        <v>6998269</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,14 +1445,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,12 +1477,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122823668</v>
+        <v>122825781</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>95903</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529038</v>
+        <v>529100</v>
       </c>
       <c r="R20" t="n">
-        <v>6998333</v>
+        <v>6998226</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2946,31 +2946,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2987,10 +2962,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122825504</v>
+        <v>122823668</v>
       </c>
       <c r="B21" t="n">
-        <v>79875</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2999,25 +2974,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3027,10 +3002,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529093</v>
+        <v>529038</v>
       </c>
       <c r="R21" t="n">
-        <v>6998292</v>
+        <v>6998333</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3079,14 +3054,24 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Sten/berg på land</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stone/rock on land</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3104,10 +3089,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122825781</v>
+        <v>122825504</v>
       </c>
       <c r="B22" t="n">
-        <v>95903</v>
+        <v>79875</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3116,25 +3101,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3144,10 +3129,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529100</v>
+        <v>529093</v>
       </c>
       <c r="R22" t="n">
-        <v>6998226</v>
+        <v>6998292</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3190,6 +3175,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -4445,10 +4445,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122826112</v>
+        <v>122825546</v>
       </c>
       <c r="B33" t="n">
-        <v>79145</v>
+        <v>79751</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4457,25 +4457,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>257107</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529127</v>
+        <v>529031</v>
       </c>
       <c r="R33" t="n">
-        <v>6998223</v>
+        <v>6998345</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4562,10 +4562,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122825546</v>
+        <v>122826113</v>
       </c>
       <c r="B34" t="n">
-        <v>79751</v>
+        <v>79876</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4578,21 +4578,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529031</v>
+        <v>529119</v>
       </c>
       <c r="R34" t="n">
-        <v>6998345</v>
+        <v>6998208</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4635,26 +4635,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4663,26 +4648,51 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122826113</v>
+        <v>122825840</v>
       </c>
       <c r="B35" t="n">
-        <v>79876</v>
+        <v>79875</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4695,21 +4705,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4719,10 +4729,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529119</v>
+        <v>529095</v>
       </c>
       <c r="R35" t="n">
-        <v>6998208</v>
+        <v>6998278</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4752,11 +4762,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På klippa i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4765,51 +4790,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122825840</v>
+        <v>122826112</v>
       </c>
       <c r="B36" t="n">
-        <v>79875</v>
+        <v>79145</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4818,25 +4818,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6461</v>
+        <v>257107</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529095</v>
+        <v>529127</v>
       </c>
       <c r="R36" t="n">
-        <v>6998278</v>
+        <v>6998223</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På klippa i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -4445,10 +4445,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122825546</v>
+        <v>122826112</v>
       </c>
       <c r="B33" t="n">
-        <v>79751</v>
+        <v>79145</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4457,25 +4457,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>257107</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529031</v>
+        <v>529127</v>
       </c>
       <c r="R33" t="n">
-        <v>6998345</v>
+        <v>6998223</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4562,10 +4562,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122826113</v>
+        <v>122825546</v>
       </c>
       <c r="B34" t="n">
-        <v>79876</v>
+        <v>79751</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4578,21 +4578,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4602,10 +4602,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529119</v>
+        <v>529031</v>
       </c>
       <c r="R34" t="n">
-        <v>6998208</v>
+        <v>6998345</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4635,11 +4635,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4648,51 +4663,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122825840</v>
+        <v>122826113</v>
       </c>
       <c r="B35" t="n">
-        <v>79875</v>
+        <v>79876</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4705,21 +4695,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4729,10 +4719,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529095</v>
+        <v>529119</v>
       </c>
       <c r="R35" t="n">
-        <v>6998278</v>
+        <v>6998208</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4762,26 +4752,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På klippa i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4790,26 +4765,51 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122826112</v>
+        <v>122825840</v>
       </c>
       <c r="B36" t="n">
-        <v>79145</v>
+        <v>79875</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4818,25 +4818,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>257107</v>
+        <v>6461</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529127</v>
+        <v>529095</v>
       </c>
       <c r="R36" t="n">
-        <v>6998223</v>
+        <v>6998278</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På klippa i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122825438</v>
+        <v>122825395</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529040</v>
+        <v>529085</v>
       </c>
       <c r="R2" t="n">
-        <v>6998249</v>
+        <v>6998292</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,26 +748,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -776,26 +761,51 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122824230</v>
+        <v>122826075</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>74847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,51 +814,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529044</v>
+        <v>529120</v>
       </c>
       <c r="R3" t="n">
-        <v>6998360</v>
+        <v>6998243</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,14 +875,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
+          <t>På ved på gammal grov björkhögstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,41 +903,16 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1046,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122825875</v>
+        <v>122824230</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1085,19 +1070,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529132</v>
+        <v>529044</v>
       </c>
       <c r="R5" t="n">
-        <v>6998196</v>
+        <v>6998360</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,7 +1121,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,6 +1132,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1158,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122825635</v>
+        <v>122826435</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,39 +1189,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529077</v>
+        <v>529156</v>
       </c>
       <c r="R6" t="n">
-        <v>6998245</v>
+        <v>6998208</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,11 +1249,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122826435</v>
+        <v>122825441</v>
       </c>
       <c r="B7" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,34 +1291,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529156</v>
+        <v>529026</v>
       </c>
       <c r="R7" t="n">
-        <v>6998208</v>
+        <v>6998251</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,6 +1356,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122825922</v>
+        <v>122825531</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,41 +1399,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529093</v>
+        <v>529096</v>
       </c>
       <c r="R8" t="n">
-        <v>6998269</v>
+        <v>6998283</v>
       </c>
       <c r="S8" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,26 +1465,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1473,23 +1478,38 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122824605</v>
+        <v>122826028</v>
       </c>
       <c r="B9" t="n">
         <v>79847</v>
@@ -1523,24 +1543,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528996</v>
+        <v>529125</v>
       </c>
       <c r="R9" t="n">
-        <v>6998338</v>
+        <v>6998223</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1621,10 +1636,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122826011</v>
+        <v>122823879</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,43 +1652,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529111</v>
+        <v>529056</v>
       </c>
       <c r="R10" t="n">
-        <v>6998222</v>
+        <v>6998335</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1703,26 +1709,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1731,26 +1722,51 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122825991</v>
+        <v>122825781</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>95903</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,21 +1779,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1787,10 +1803,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529105</v>
+        <v>529100</v>
       </c>
       <c r="R11" t="n">
-        <v>6998247</v>
+        <v>6998226</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,24 +1836,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,22 +1853,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122826028</v>
+        <v>122823485</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1880,37 +1881,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529125</v>
+        <v>529041</v>
       </c>
       <c r="R12" t="n">
-        <v>6998223</v>
+        <v>6998374</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1942,6 +1948,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1953,27 +1964,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1991,7 +2002,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122826095</v>
+        <v>122825922</v>
       </c>
       <c r="B13" t="n">
         <v>79847</v>
@@ -2031,13 +2042,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529130</v>
+        <v>529093</v>
       </c>
       <c r="R13" t="n">
-        <v>6998225</v>
+        <v>6998269</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2066,7 +2077,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2076,12 +2087,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,22 +2107,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122825395</v>
+        <v>122826011</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2124,37 +2135,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529085</v>
+        <v>529111</v>
       </c>
       <c r="R14" t="n">
-        <v>6998292</v>
+        <v>6998222</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2181,11 +2201,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2194,51 +2229,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122825432</v>
+        <v>122825731</v>
       </c>
       <c r="B15" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,34 +2261,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529040</v>
+        <v>529058</v>
       </c>
       <c r="R15" t="n">
-        <v>6998249</v>
+        <v>6998331</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2310,7 +2329,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2320,12 +2339,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2352,10 +2371,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122823649</v>
+        <v>122824605</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2368,27 +2387,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2397,13 +2416,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529030</v>
+        <v>528996</v>
       </c>
       <c r="R16" t="n">
-        <v>6998340</v>
+        <v>6998338</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2435,11 +2454,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Långväxta fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2456,12 +2470,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -2471,7 +2485,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2489,10 +2503,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122823879</v>
+        <v>122826113</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2501,25 +2515,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2529,13 +2543,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529056</v>
+        <v>529119</v>
       </c>
       <c r="R17" t="n">
-        <v>6998335</v>
+        <v>6998208</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2578,27 +2592,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2616,10 +2630,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122826075</v>
+        <v>122825438</v>
       </c>
       <c r="B18" t="n">
-        <v>74847</v>
+        <v>78503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2628,25 +2642,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6439</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2656,13 +2670,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529120</v>
+        <v>529040</v>
       </c>
       <c r="R18" t="n">
-        <v>6998243</v>
+        <v>6998249</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2691,7 +2705,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2701,12 +2715,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På ved på gammal grov björkhögstubbe</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2733,10 +2747,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122824790</v>
+        <v>122825635</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2749,34 +2763,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528970</v>
+        <v>529077</v>
       </c>
       <c r="R19" t="n">
-        <v>6998415</v>
+        <v>6998245</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2811,6 +2830,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2819,31 +2843,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2860,10 +2859,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122825781</v>
+        <v>122823649</v>
       </c>
       <c r="B20" t="n">
-        <v>95903</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2876,37 +2875,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529100</v>
+        <v>529030</v>
       </c>
       <c r="R20" t="n">
-        <v>6998226</v>
+        <v>6998340</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2938,6 +2942,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långväxta fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2946,6 +2955,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2962,7 +2996,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122823668</v>
+        <v>122824740</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -3002,10 +3036,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529038</v>
+        <v>528995</v>
       </c>
       <c r="R21" t="n">
-        <v>6998333</v>
+        <v>6998368</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3040,6 +3074,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3056,22 +3095,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3206,10 +3245,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122824434</v>
+        <v>122824790</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3222,39 +3261,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529000</v>
+        <v>528970</v>
       </c>
       <c r="R23" t="n">
-        <v>6998335</v>
+        <v>6998415</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3289,11 +3323,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3310,12 +3339,12 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -3325,7 +3354,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3343,10 +3372,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122825983</v>
+        <v>122826112</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>79145</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3359,21 +3388,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>257107</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3383,13 +3412,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529112</v>
+        <v>529127</v>
       </c>
       <c r="R24" t="n">
-        <v>6998258</v>
+        <v>6998223</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3416,14 +3445,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3434,51 +3473,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122825731</v>
+        <v>122826095</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3491,46 +3505,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529058</v>
+        <v>529130</v>
       </c>
       <c r="R25" t="n">
-        <v>6998331</v>
+        <v>6998225</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3559,7 +3564,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3569,12 +3574,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3589,19 +3594,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122825639</v>
+        <v>122823668</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3641,13 +3646,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529113</v>
+        <v>529038</v>
       </c>
       <c r="R26" t="n">
-        <v>6998294</v>
+        <v>6998333</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3728,10 +3733,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122825401</v>
+        <v>122825639</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3744,42 +3749,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529023</v>
+        <v>529113</v>
       </c>
       <c r="R27" t="n">
-        <v>6998251</v>
+        <v>6998294</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3811,11 +3811,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3824,6 +3819,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3840,10 +3860,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122825664</v>
+        <v>122825840</v>
       </c>
       <c r="B28" t="n">
-        <v>74863</v>
+        <v>79875</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3852,25 +3872,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6461</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3880,10 +3900,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529058</v>
+        <v>529095</v>
       </c>
       <c r="R28" t="n">
-        <v>6998341</v>
+        <v>6998278</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3915,7 +3935,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3925,12 +3945,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På klippa i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3957,10 +3977,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122823202</v>
+        <v>122825432</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3973,21 +3993,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3997,10 +4017,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529003</v>
+        <v>529040</v>
       </c>
       <c r="R29" t="n">
-        <v>6998380</v>
+        <v>6998249</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4030,11 +4050,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4043,51 +4078,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122823485</v>
+        <v>122825664</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4100,42 +4110,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529041</v>
+        <v>529058</v>
       </c>
       <c r="R30" t="n">
-        <v>6998374</v>
+        <v>6998341</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4162,14 +4167,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4180,51 +4195,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122825497</v>
+        <v>122823202</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4237,21 +4227,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4261,10 +4251,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529024</v>
+        <v>529003</v>
       </c>
       <c r="R31" t="n">
-        <v>6998262</v>
+        <v>6998380</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4307,6 +4297,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4323,10 +4338,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122825531</v>
+        <v>122825401</v>
       </c>
       <c r="B32" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4335,31 +4350,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4368,13 +4383,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529096</v>
+        <v>529023</v>
       </c>
       <c r="R32" t="n">
-        <v>6998283</v>
+        <v>6998251</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4406,6 +4421,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4414,21 +4434,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4445,10 +4450,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122826112</v>
+        <v>122825546</v>
       </c>
       <c r="B33" t="n">
-        <v>79145</v>
+        <v>79751</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4457,25 +4462,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>257107</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4485,10 +4490,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529127</v>
+        <v>529031</v>
       </c>
       <c r="R33" t="n">
-        <v>6998223</v>
+        <v>6998345</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4520,7 +4525,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4530,7 +4535,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4562,10 +4567,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122825546</v>
+        <v>122824569</v>
       </c>
       <c r="B34" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4574,25 +4579,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4602,13 +4607,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529031</v>
+        <v>528994</v>
       </c>
       <c r="R34" t="n">
-        <v>6998345</v>
+        <v>6998342</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4635,24 +4640,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Lunglav på gran intill en asp med lunglav.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4663,26 +4658,51 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122826113</v>
+        <v>122825738</v>
       </c>
       <c r="B35" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4691,41 +4711,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529119</v>
+        <v>529116</v>
       </c>
       <c r="R35" t="n">
-        <v>6998208</v>
+        <v>6998284</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4752,11 +4781,21 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4765,51 +4804,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122825840</v>
+        <v>122825588</v>
       </c>
       <c r="B36" t="n">
-        <v>79875</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4818,25 +4832,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4846,10 +4860,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529095</v>
+        <v>529032</v>
       </c>
       <c r="R36" t="n">
-        <v>6998278</v>
+        <v>6998357</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4881,7 +4895,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4891,12 +4905,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På klippa i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4923,7 +4937,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122824569</v>
+        <v>122825991</v>
       </c>
       <c r="B37" t="n">
         <v>79847</v>
@@ -4963,13 +4977,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528994</v>
+        <v>529105</v>
       </c>
       <c r="R37" t="n">
-        <v>6998342</v>
+        <v>6998247</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4996,14 +5010,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Lunglav på gran intill en asp med lunglav.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5014,51 +5038,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122825738</v>
+        <v>122824434</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5071,31 +5070,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5104,13 +5099,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529116</v>
+        <v>529000</v>
       </c>
       <c r="R38" t="n">
-        <v>6998284</v>
+        <v>6998335</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5137,19 +5132,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:02</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5160,23 +5150,48 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122825588</v>
+        <v>122825983</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -5216,13 +5231,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529032</v>
+        <v>529112</v>
       </c>
       <c r="R39" t="n">
-        <v>6998357</v>
+        <v>6998258</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5249,24 +5264,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5277,26 +5282,51 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122824740</v>
+        <v>122825497</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5309,21 +5339,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5333,10 +5363,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528995</v>
+        <v>529024</v>
       </c>
       <c r="R40" t="n">
-        <v>6998368</v>
+        <v>6998262</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5371,11 +5401,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5384,31 +5409,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5425,7 +5425,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122825441</v>
+        <v>122825875</v>
       </c>
       <c r="B41" t="n">
         <v>57478</v>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529026</v>
+        <v>529132</v>
       </c>
       <c r="R41" t="n">
-        <v>6998251</v>
+        <v>6998196</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -2503,10 +2503,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122826113</v>
+        <v>122825438</v>
       </c>
       <c r="B17" t="n">
-        <v>79876</v>
+        <v>78503</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2515,25 +2515,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529119</v>
+        <v>529040</v>
       </c>
       <c r="R17" t="n">
-        <v>6998208</v>
+        <v>6998249</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2576,11 +2576,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2589,51 +2604,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122825438</v>
+        <v>122826113</v>
       </c>
       <c r="B18" t="n">
-        <v>78503</v>
+        <v>79876</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2642,25 +2632,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2670,10 +2660,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529040</v>
+        <v>529119</v>
       </c>
       <c r="R18" t="n">
-        <v>6998249</v>
+        <v>6998208</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2703,26 +2693,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2731,16 +2706,41 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -5191,10 +5191,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122825983</v>
+        <v>122825875</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5207,37 +5207,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529112</v>
+        <v>529132</v>
       </c>
       <c r="R39" t="n">
-        <v>6998258</v>
+        <v>6998196</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5271,7 +5276,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5282,31 +5287,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5425,10 +5405,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122825875</v>
+        <v>122825983</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5441,42 +5421,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529132</v>
+        <v>529112</v>
       </c>
       <c r="R41" t="n">
-        <v>6998196</v>
+        <v>6998258</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5510,7 +5485,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5521,6 +5496,31 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -2503,10 +2503,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122825438</v>
+        <v>122826113</v>
       </c>
       <c r="B17" t="n">
-        <v>78503</v>
+        <v>79876</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2515,25 +2515,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529040</v>
+        <v>529119</v>
       </c>
       <c r="R17" t="n">
-        <v>6998249</v>
+        <v>6998208</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2576,26 +2576,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2604,26 +2589,51 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122826113</v>
+        <v>122825438</v>
       </c>
       <c r="B18" t="n">
-        <v>79876</v>
+        <v>78503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,25 +2642,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2660,10 +2670,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529119</v>
+        <v>529040</v>
       </c>
       <c r="R18" t="n">
-        <v>6998208</v>
+        <v>6998249</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2693,11 +2703,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2706,41 +2731,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -5191,10 +5191,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122825875</v>
+        <v>122825983</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5207,42 +5207,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529132</v>
+        <v>529112</v>
       </c>
       <c r="R39" t="n">
-        <v>6998196</v>
+        <v>6998258</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5276,7 +5271,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5287,6 +5282,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5405,10 +5425,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122825983</v>
+        <v>122825875</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5421,37 +5441,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529112</v>
+        <v>529132</v>
       </c>
       <c r="R41" t="n">
-        <v>6998258</v>
+        <v>6998196</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5485,7 +5510,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5496,31 +5521,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122825395</v>
+        <v>122826028</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529085</v>
+        <v>529125</v>
       </c>
       <c r="R2" t="n">
-        <v>6998292</v>
+        <v>6998223</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,22 +769,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122826075</v>
+        <v>122825395</v>
       </c>
       <c r="B3" t="n">
-        <v>74847</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,25 +814,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529120</v>
+        <v>529085</v>
       </c>
       <c r="R3" t="n">
-        <v>6998243</v>
+        <v>6998292</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,26 +875,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På ved på gammal grov björkhögstubbe</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -903,23 +888,48 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122825467</v>
+        <v>122825401</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -955,7 +965,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529022</v>
+        <v>529023</v>
       </c>
       <c r="R4" t="n">
-        <v>6998263</v>
+        <v>6998251</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,7 +1014,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122824230</v>
+        <v>122826435</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,47 +1057,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529044</v>
+        <v>529156</v>
       </c>
       <c r="R5" t="n">
-        <v>6998360</v>
+        <v>6998208</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,11 +1119,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1132,31 +1127,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1173,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122826435</v>
+        <v>122823202</v>
       </c>
       <c r="B6" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1213,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529156</v>
+        <v>529003</v>
       </c>
       <c r="R6" t="n">
-        <v>6998208</v>
+        <v>6998380</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,6 +1229,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1275,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122825441</v>
+        <v>122825531</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,31 +1282,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1320,13 +1315,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529026</v>
+        <v>529096</v>
       </c>
       <c r="R7" t="n">
-        <v>6998251</v>
+        <v>6998283</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1358,11 +1353,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1371,6 +1361,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1387,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122825531</v>
+        <v>122825840</v>
       </c>
       <c r="B8" t="n">
-        <v>79876</v>
+        <v>79875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,42 +1408,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529096</v>
+        <v>529095</v>
       </c>
       <c r="R8" t="n">
-        <v>6998283</v>
+        <v>6998278</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1465,11 +1465,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På klippa i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1478,41 +1493,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122826028</v>
+        <v>122824230</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,37 +1525,47 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529125</v>
+        <v>529044</v>
       </c>
       <c r="R9" t="n">
-        <v>6998223</v>
+        <v>6998360</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1587,6 +1597,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1598,27 +1613,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1636,7 +1651,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122823879</v>
+        <v>122824740</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1676,13 +1691,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529056</v>
+        <v>528995</v>
       </c>
       <c r="R10" t="n">
-        <v>6998335</v>
+        <v>6998368</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1714,6 +1729,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1725,7 +1745,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1763,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122825781</v>
+        <v>122825467</v>
       </c>
       <c r="B11" t="n">
-        <v>95903</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1779,34 +1799,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529100</v>
+        <v>529022</v>
       </c>
       <c r="R11" t="n">
-        <v>6998226</v>
+        <v>6998263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1839,6 +1864,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122823485</v>
+        <v>122825781</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>95911</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1881,42 +1911,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529041</v>
+        <v>529100</v>
       </c>
       <c r="R12" t="n">
-        <v>6998374</v>
+        <v>6998226</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1948,11 +1973,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1961,31 +1981,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2002,10 +1997,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122825922</v>
+        <v>122825738</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2018,37 +2013,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529093</v>
+        <v>529116</v>
       </c>
       <c r="R13" t="n">
-        <v>6998269</v>
+        <v>6998284</v>
       </c>
       <c r="S13" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2077,7 +2081,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2087,12 +2091,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2107,22 +2106,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122826011</v>
+        <v>122825639</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2135,46 +2134,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529111</v>
+        <v>529113</v>
       </c>
       <c r="R14" t="n">
-        <v>6998222</v>
+        <v>6998294</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2201,26 +2191,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2229,26 +2204,51 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122825731</v>
+        <v>122826112</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>79145</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2261,43 +2261,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>257107</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>S.Ekman</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529058</v>
+        <v>529127</v>
       </c>
       <c r="R15" t="n">
-        <v>6998331</v>
+        <v>6998223</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2329,7 +2320,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2339,12 +2330,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2371,7 +2362,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122824605</v>
+        <v>122824434</v>
       </c>
       <c r="B16" t="n">
         <v>79847</v>
@@ -2407,7 +2398,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2416,13 +2407,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528996</v>
+        <v>529000</v>
       </c>
       <c r="R16" t="n">
-        <v>6998338</v>
+        <v>6998335</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2452,6 +2443,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2503,10 +2499,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122826113</v>
+        <v>122826095</v>
       </c>
       <c r="B17" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2515,25 +2511,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2543,13 +2539,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529119</v>
+        <v>529130</v>
       </c>
       <c r="R17" t="n">
-        <v>6998208</v>
+        <v>6998225</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2576,11 +2572,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2589,51 +2600,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122825438</v>
+        <v>122826011</v>
       </c>
       <c r="B18" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2646,37 +2632,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529040</v>
+        <v>529111</v>
       </c>
       <c r="R18" t="n">
-        <v>6998249</v>
+        <v>6998222</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2705,7 +2700,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2715,12 +2710,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2735,22 +2730,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122825635</v>
+        <v>122825588</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2763,39 +2758,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529077</v>
+        <v>529032</v>
       </c>
       <c r="R19" t="n">
-        <v>6998245</v>
+        <v>6998357</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2825,14 +2815,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2847,19 +2847,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122823649</v>
+        <v>122823485</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2904,13 +2904,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529030</v>
+        <v>529041</v>
       </c>
       <c r="R20" t="n">
-        <v>6998340</v>
+        <v>6998374</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar.</t>
+          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2958,27 +2958,27 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122824740</v>
+        <v>122825991</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3012,21 +3012,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3036,10 +3036,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528995</v>
+        <v>529105</v>
       </c>
       <c r="R21" t="n">
-        <v>6998368</v>
+        <v>6998247</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3069,14 +3069,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3087,51 +3097,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122825504</v>
+        <v>122825983</v>
       </c>
       <c r="B22" t="n">
-        <v>79875</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3140,25 +3125,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3168,13 +3153,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529093</v>
+        <v>529112</v>
       </c>
       <c r="R22" t="n">
-        <v>6998292</v>
+        <v>6998258</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3206,6 +3191,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3220,14 +3210,24 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Sten/berg på land</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stone/rock on land</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3245,10 +3245,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122824790</v>
+        <v>122825664</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3261,21 +3261,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528970</v>
+        <v>529058</v>
       </c>
       <c r="R23" t="n">
-        <v>6998415</v>
+        <v>6998341</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3318,11 +3318,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3331,51 +3346,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122826112</v>
+        <v>122825731</v>
       </c>
       <c r="B24" t="n">
-        <v>79145</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3388,34 +3378,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>257107</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529127</v>
+        <v>529058</v>
       </c>
       <c r="R24" t="n">
-        <v>6998223</v>
+        <v>6998331</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3447,7 +3446,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3457,12 +3456,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3489,10 +3488,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122826095</v>
+        <v>122825546</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3501,25 +3500,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3529,13 +3528,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529130</v>
+        <v>529031</v>
       </c>
       <c r="R25" t="n">
-        <v>6998225</v>
+        <v>6998345</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3564,7 +3563,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3574,12 +3573,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3594,22 +3593,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122823668</v>
+        <v>122824569</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3622,21 +3621,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3646,13 +3645,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529038</v>
+        <v>528994</v>
       </c>
       <c r="R26" t="n">
-        <v>6998333</v>
+        <v>6998342</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3684,6 +3683,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Lunglav på gran intill en asp med lunglav.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3700,22 +3704,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3733,10 +3737,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122825639</v>
+        <v>122826113</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3745,25 +3749,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3773,13 +3777,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529113</v>
+        <v>529119</v>
       </c>
       <c r="R27" t="n">
-        <v>6998294</v>
+        <v>6998208</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3827,12 +3831,12 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -3842,7 +3846,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3860,7 +3864,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122825840</v>
+        <v>122825504</v>
       </c>
       <c r="B28" t="n">
         <v>79875</v>
@@ -3900,10 +3904,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529095</v>
+        <v>529093</v>
       </c>
       <c r="R28" t="n">
-        <v>6998278</v>
+        <v>6998292</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3933,26 +3937,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På klippa i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3961,26 +3950,41 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122825432</v>
+        <v>122823649</v>
       </c>
       <c r="B29" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3993,37 +3997,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529040</v>
+        <v>529030</v>
       </c>
       <c r="R29" t="n">
-        <v>6998249</v>
+        <v>6998340</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4050,24 +4059,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>Långväxta fertila bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4078,26 +4077,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122825664</v>
+        <v>122825497</v>
       </c>
       <c r="B30" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4110,21 +4134,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4134,10 +4158,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529058</v>
+        <v>529024</v>
       </c>
       <c r="R30" t="n">
-        <v>6998341</v>
+        <v>6998262</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4167,24 +4191,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4199,22 +4208,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122823202</v>
+        <v>122825438</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4227,21 +4236,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4251,10 +4260,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529003</v>
+        <v>529040</v>
       </c>
       <c r="R31" t="n">
-        <v>6998380</v>
+        <v>6998249</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4284,11 +4293,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4297,51 +4321,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122825401</v>
+        <v>122823879</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4354,42 +4353,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529023</v>
+        <v>529056</v>
       </c>
       <c r="R32" t="n">
-        <v>6998251</v>
+        <v>6998335</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4421,11 +4415,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4434,6 +4423,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4450,10 +4464,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122825546</v>
+        <v>122825635</v>
       </c>
       <c r="B33" t="n">
-        <v>79751</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4462,38 +4476,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529031</v>
+        <v>529077</v>
       </c>
       <c r="R33" t="n">
-        <v>6998345</v>
+        <v>6998245</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4523,24 +4542,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4555,22 +4564,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122824569</v>
+        <v>122823668</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4583,21 +4592,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4607,13 +4616,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528994</v>
+        <v>529038</v>
       </c>
       <c r="R34" t="n">
-        <v>6998342</v>
+        <v>6998333</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4645,11 +4654,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Lunglav på gran intill en asp med lunglav.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4666,22 +4670,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4699,10 +4703,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122825738</v>
+        <v>122825922</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4715,46 +4719,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529116</v>
+        <v>529093</v>
       </c>
       <c r="R35" t="n">
-        <v>6998284</v>
+        <v>6998269</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4783,7 +4778,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4793,7 +4788,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4808,22 +4808,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122825588</v>
+        <v>122824605</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4836,37 +4836,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529032</v>
+        <v>528996</v>
       </c>
       <c r="R36" t="n">
-        <v>6998357</v>
+        <v>6998338</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4893,26 +4898,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4921,26 +4911,51 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122825991</v>
+        <v>122825432</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4953,21 +4968,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4977,10 +4992,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529105</v>
+        <v>529040</v>
       </c>
       <c r="R37" t="n">
-        <v>6998247</v>
+        <v>6998249</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5012,7 +5027,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5022,12 +5037,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5054,10 +5069,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122824434</v>
+        <v>122825875</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5070,27 +5085,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5099,10 +5114,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529000</v>
+        <v>529132</v>
       </c>
       <c r="R38" t="n">
-        <v>6998335</v>
+        <v>6998196</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5139,7 +5154,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5150,31 +5165,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5191,10 +5181,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122825983</v>
+        <v>122825441</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5207,37 +5197,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529112</v>
+        <v>529026</v>
       </c>
       <c r="R39" t="n">
-        <v>6998258</v>
+        <v>6998251</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5271,7 +5266,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5282,31 +5277,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5323,10 +5293,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122825497</v>
+        <v>122826075</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>74847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5335,25 +5305,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5363,13 +5333,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529024</v>
+        <v>529120</v>
       </c>
       <c r="R40" t="n">
-        <v>6998262</v>
+        <v>6998243</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5396,9 +5366,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På ved på gammal grov björkhögstubbe</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5413,22 +5398,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122825875</v>
+        <v>122824790</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5441,39 +5426,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529132</v>
+        <v>528970</v>
       </c>
       <c r="R41" t="n">
-        <v>6998196</v>
+        <v>6998415</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5508,11 +5488,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5521,6 +5496,31 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -2245,10 +2245,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122826112</v>
+        <v>122824434</v>
       </c>
       <c r="B15" t="n">
-        <v>79145</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2261,34 +2261,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>257107</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529127</v>
+        <v>529000</v>
       </c>
       <c r="R15" t="n">
-        <v>6998223</v>
+        <v>6998335</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2318,24 +2323,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2346,26 +2341,51 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122824434</v>
+        <v>122826112</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>79145</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2378,39 +2398,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>257107</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529000</v>
+        <v>529127</v>
       </c>
       <c r="R16" t="n">
-        <v>6998335</v>
+        <v>6998223</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2440,14 +2455,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2458,41 +2483,16 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -4464,10 +4464,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122825635</v>
+        <v>122823668</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4480,39 +4480,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529077</v>
+        <v>529038</v>
       </c>
       <c r="R33" t="n">
-        <v>6998245</v>
+        <v>6998333</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4547,11 +4542,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4560,6 +4550,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4576,10 +4591,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122823668</v>
+        <v>122825635</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4592,34 +4607,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529038</v>
+        <v>529077</v>
       </c>
       <c r="R34" t="n">
-        <v>6998333</v>
+        <v>6998245</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4654,6 +4674,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4662,31 +4687,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4703,7 +4703,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122825922</v>
+        <v>122824605</v>
       </c>
       <c r="B35" t="n">
         <v>79847</v>
@@ -4737,19 +4737,24 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529093</v>
+        <v>528996</v>
       </c>
       <c r="R35" t="n">
-        <v>6998269</v>
+        <v>6998338</v>
       </c>
       <c r="S35" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4776,26 +4781,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4804,23 +4794,48 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122824605</v>
+        <v>122825922</v>
       </c>
       <c r="B36" t="n">
         <v>79847</v>
@@ -4854,24 +4869,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528996</v>
+        <v>529093</v>
       </c>
       <c r="R36" t="n">
-        <v>6998338</v>
+        <v>6998269</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4898,11 +4908,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4911,41 +4936,16 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122826028</v>
+        <v>122826095</v>
       </c>
       <c r="B2" t="n">
         <v>79847</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529125</v>
+        <v>529130</v>
       </c>
       <c r="R2" t="n">
-        <v>6998223</v>
+        <v>6998225</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,11 +748,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,51 +776,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122825395</v>
+        <v>122825875</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529085</v>
+        <v>529132</v>
       </c>
       <c r="R3" t="n">
-        <v>6998292</v>
+        <v>6998196</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,6 +875,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -888,31 +888,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -929,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122825401</v>
+        <v>122826075</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>74847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,46 +916,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529023</v>
+        <v>529120</v>
       </c>
       <c r="R4" t="n">
-        <v>6998251</v>
+        <v>6998243</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,14 +977,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På ved på gammal grov björkhögstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122826435</v>
+        <v>122825635</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529156</v>
+        <v>529077</v>
       </c>
       <c r="R5" t="n">
-        <v>6998208</v>
+        <v>6998245</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,6 +1102,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122823202</v>
+        <v>122825922</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,13 +1173,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529003</v>
+        <v>529093</v>
       </c>
       <c r="R6" t="n">
-        <v>6998380</v>
+        <v>6998269</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,11 +1206,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1229,48 +1234,23 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122825531</v>
+        <v>122826113</v>
       </c>
       <c r="B7" t="n">
         <v>79876</v>
@@ -1304,24 +1284,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529096</v>
+        <v>529119</v>
       </c>
       <c r="R7" t="n">
-        <v>6998283</v>
+        <v>6998208</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1367,14 +1342,24 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Sten/berg på land</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stone/rock on land</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1392,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122825840</v>
+        <v>122824790</v>
       </c>
       <c r="B8" t="n">
-        <v>79875</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,25 +1389,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1432,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529095</v>
+        <v>528970</v>
       </c>
       <c r="R8" t="n">
-        <v>6998278</v>
+        <v>6998415</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,26 +1450,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På klippa i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1493,26 +1463,51 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122824230</v>
+        <v>122825504</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>79875</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,51 +1516,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529044</v>
+        <v>529093</v>
       </c>
       <c r="R9" t="n">
-        <v>6998360</v>
+        <v>6998292</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,11 +1582,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1613,27 +1593,17 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1651,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122824740</v>
+        <v>122825531</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1663,41 +1633,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528995</v>
+        <v>529096</v>
       </c>
       <c r="R10" t="n">
-        <v>6998368</v>
+        <v>6998283</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1729,11 +1704,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1748,24 +1718,14 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1783,7 +1743,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122825467</v>
+        <v>122825441</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1828,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529022</v>
+        <v>529026</v>
       </c>
       <c r="R11" t="n">
-        <v>6998263</v>
+        <v>6998251</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1868,7 +1828,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122825781</v>
+        <v>122825588</v>
       </c>
       <c r="B12" t="n">
-        <v>95911</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,21 +1871,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1935,10 +1895,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529100</v>
+        <v>529032</v>
       </c>
       <c r="R12" t="n">
-        <v>6998226</v>
+        <v>6998357</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1968,9 +1928,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1985,22 +1960,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122825738</v>
+        <v>122824605</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,31 +1988,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2046,13 +2017,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529116</v>
+        <v>528996</v>
       </c>
       <c r="R13" t="n">
-        <v>6998284</v>
+        <v>6998338</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2079,21 +2050,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2102,26 +2063,51 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122825639</v>
+        <v>122825497</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2134,21 +2120,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2158,13 +2144,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529113</v>
+        <v>529024</v>
       </c>
       <c r="R14" t="n">
-        <v>6998294</v>
+        <v>6998262</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2204,31 +2190,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2245,7 +2206,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122824434</v>
+        <v>122824569</v>
       </c>
       <c r="B15" t="n">
         <v>79847</v>
@@ -2279,24 +2240,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529000</v>
+        <v>528994</v>
       </c>
       <c r="R15" t="n">
-        <v>6998335</v>
+        <v>6998342</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2330,7 +2286,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
+          <t>Lunglav på gran intill en asp med lunglav.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2349,22 +2305,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2382,10 +2338,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122826112</v>
+        <v>122825546</v>
       </c>
       <c r="B16" t="n">
-        <v>79145</v>
+        <v>79751</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2394,25 +2350,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>257107</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2422,10 +2378,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529127</v>
+        <v>529031</v>
       </c>
       <c r="R16" t="n">
-        <v>6998223</v>
+        <v>6998345</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2457,7 +2413,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2467,7 +2423,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2499,10 +2455,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122826095</v>
+        <v>122824740</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2515,21 +2471,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2539,13 +2495,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529130</v>
+        <v>528995</v>
       </c>
       <c r="R17" t="n">
-        <v>6998225</v>
+        <v>6998368</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2572,24 +2528,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2600,26 +2546,51 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122826011</v>
+        <v>122825432</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,46 +2603,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529111</v>
+        <v>529040</v>
       </c>
       <c r="R18" t="n">
-        <v>6998222</v>
+        <v>6998249</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2700,7 +2662,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2710,12 +2672,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2730,19 +2692,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122825588</v>
+        <v>122825731</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2775,17 +2737,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529032</v>
+        <v>529058</v>
       </c>
       <c r="R19" t="n">
-        <v>6998357</v>
+        <v>6998331</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2817,7 +2788,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2827,7 +2798,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2859,10 +2830,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122823485</v>
+        <v>122825401</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2875,27 +2846,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2904,13 +2875,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529041</v>
+        <v>529023</v>
       </c>
       <c r="R20" t="n">
-        <v>6998374</v>
+        <v>6998251</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2944,7 +2915,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2955,31 +2926,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2996,10 +2942,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122825991</v>
+        <v>122826435</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3012,21 +2958,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3036,10 +2982,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529105</v>
+        <v>529156</v>
       </c>
       <c r="R21" t="n">
-        <v>6998247</v>
+        <v>6998208</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3069,24 +3015,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3101,22 +3032,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122825983</v>
+        <v>122825781</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>95911</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3129,21 +3060,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3153,13 +3084,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529112</v>
+        <v>529100</v>
       </c>
       <c r="R22" t="n">
-        <v>6998258</v>
+        <v>6998226</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3191,11 +3122,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3204,31 +3130,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3245,10 +3146,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122825664</v>
+        <v>122826011</v>
       </c>
       <c r="B23" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3261,37 +3162,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529058</v>
+        <v>529111</v>
       </c>
       <c r="R23" t="n">
-        <v>6998341</v>
+        <v>6998222</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3320,7 +3230,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3330,12 +3240,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3350,22 +3260,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122825731</v>
+        <v>122824434</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3378,31 +3288,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3411,10 +3317,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529058</v>
+        <v>529000</v>
       </c>
       <c r="R24" t="n">
-        <v>6998331</v>
+        <v>6998335</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3444,24 +3350,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3472,26 +3368,51 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122825546</v>
+        <v>122826112</v>
       </c>
       <c r="B25" t="n">
-        <v>79751</v>
+        <v>79145</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3500,25 +3421,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>257107</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3528,10 +3449,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529031</v>
+        <v>529127</v>
       </c>
       <c r="R25" t="n">
-        <v>6998345</v>
+        <v>6998223</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3563,7 +3484,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3573,7 +3494,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3605,10 +3526,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122824569</v>
+        <v>122825840</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>79875</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3617,25 +3538,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3645,13 +3566,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528994</v>
+        <v>529095</v>
       </c>
       <c r="R26" t="n">
-        <v>6998342</v>
+        <v>6998278</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3678,14 +3599,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Lunglav på gran intill en asp med lunglav.</t>
+          <t>På klippa i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3696,51 +3627,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122826113</v>
+        <v>122823202</v>
       </c>
       <c r="B27" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3749,25 +3655,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3777,10 +3683,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529119</v>
+        <v>529003</v>
       </c>
       <c r="R27" t="n">
-        <v>6998208</v>
+        <v>6998380</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3826,27 +3732,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3864,10 +3770,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122825504</v>
+        <v>122823485</v>
       </c>
       <c r="B28" t="n">
-        <v>79875</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3876,41 +3782,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529093</v>
+        <v>529041</v>
       </c>
       <c r="R28" t="n">
-        <v>6998292</v>
+        <v>6998374</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3942,6 +3853,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3953,17 +3869,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Sten/berg på land</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stone/rock on land</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3981,10 +3907,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122823649</v>
+        <v>122825438</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3997,42 +3923,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529030</v>
+        <v>529040</v>
       </c>
       <c r="R29" t="n">
-        <v>6998340</v>
+        <v>6998249</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4059,14 +3980,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar.</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4077,48 +4008,23 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122825497</v>
+        <v>122826028</v>
       </c>
       <c r="B30" t="n">
         <v>79847</v>
@@ -4158,13 +4064,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529024</v>
+        <v>529125</v>
       </c>
       <c r="R30" t="n">
-        <v>6998262</v>
+        <v>6998223</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4204,6 +4110,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4220,10 +4151,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122825438</v>
+        <v>122823668</v>
       </c>
       <c r="B31" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4236,21 +4167,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4260,10 +4191,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529040</v>
+        <v>529038</v>
       </c>
       <c r="R31" t="n">
-        <v>6998249</v>
+        <v>6998333</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4293,26 +4224,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4321,23 +4237,48 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122823879</v>
+        <v>122823649</v>
       </c>
       <c r="B32" t="n">
         <v>78766</v>
@@ -4371,19 +4312,24 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529056</v>
+        <v>529030</v>
       </c>
       <c r="R32" t="n">
-        <v>6998335</v>
+        <v>6998340</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4415,6 +4361,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Långväxta fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4426,27 +4377,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4464,10 +4415,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122823668</v>
+        <v>122825467</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4480,34 +4431,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529038</v>
+        <v>529022</v>
       </c>
       <c r="R33" t="n">
-        <v>6998333</v>
+        <v>6998263</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4542,6 +4498,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4550,31 +4511,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4591,10 +4527,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122825635</v>
+        <v>122823879</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4607,42 +4543,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529077</v>
+        <v>529056</v>
       </c>
       <c r="R34" t="n">
-        <v>6998245</v>
+        <v>6998335</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4674,11 +4605,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4687,6 +4613,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4703,10 +4654,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122824605</v>
+        <v>122825738</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4719,27 +4670,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4748,13 +4703,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528996</v>
+        <v>529116</v>
       </c>
       <c r="R35" t="n">
-        <v>6998338</v>
+        <v>6998284</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4781,11 +4736,21 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4794,51 +4759,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122825922</v>
+        <v>122825395</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4851,21 +4791,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4875,13 +4815,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529093</v>
+        <v>529085</v>
       </c>
       <c r="R36" t="n">
-        <v>6998269</v>
+        <v>6998292</v>
       </c>
       <c r="S36" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4908,26 +4848,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4936,26 +4861,51 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122825432</v>
+        <v>122824230</v>
       </c>
       <c r="B37" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4968,37 +4918,47 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529040</v>
+        <v>529044</v>
       </c>
       <c r="R37" t="n">
-        <v>6998249</v>
+        <v>6998360</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5025,24 +4985,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5053,26 +5003,51 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122825875</v>
+        <v>122825991</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5085,39 +5060,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529132</v>
+        <v>529105</v>
       </c>
       <c r="R38" t="n">
-        <v>6998196</v>
+        <v>6998247</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5147,14 +5117,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5169,22 +5149,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122825441</v>
+        <v>122825983</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5197,42 +5177,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529026</v>
+        <v>529112</v>
       </c>
       <c r="R39" t="n">
-        <v>6998251</v>
+        <v>6998258</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5266,7 +5241,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5277,6 +5252,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5293,10 +5293,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122826075</v>
+        <v>122825664</v>
       </c>
       <c r="B40" t="n">
-        <v>74847</v>
+        <v>74863</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5305,25 +5305,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5333,13 +5333,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529120</v>
+        <v>529058</v>
       </c>
       <c r="R40" t="n">
-        <v>6998243</v>
+        <v>6998341</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På ved på gammal grov björkhögstubbe</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5410,7 +5410,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122824790</v>
+        <v>122825639</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -5450,13 +5450,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528970</v>
+        <v>529113</v>
       </c>
       <c r="R41" t="n">
-        <v>6998415</v>
+        <v>6998294</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -4024,10 +4024,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122826028</v>
+        <v>122823668</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4040,21 +4040,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529125</v>
+        <v>529038</v>
       </c>
       <c r="R30" t="n">
-        <v>6998223</v>
+        <v>6998333</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4118,12 +4118,12 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122823668</v>
+        <v>122823649</v>
       </c>
       <c r="B31" t="n">
         <v>78766</v>
@@ -4185,19 +4185,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529038</v>
+        <v>529030</v>
       </c>
       <c r="R31" t="n">
-        <v>6998333</v>
+        <v>6998340</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4229,6 +4234,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Långväxta fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4245,12 +4255,12 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -4260,7 +4270,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4278,10 +4288,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122823649</v>
+        <v>122825467</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4294,27 +4304,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4323,13 +4333,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529030</v>
+        <v>529022</v>
       </c>
       <c r="R32" t="n">
-        <v>6998340</v>
+        <v>6998263</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4363,7 +4373,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4374,31 +4384,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4415,10 +4400,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122825467</v>
+        <v>122826028</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4431,42 +4416,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529022</v>
+        <v>529125</v>
       </c>
       <c r="R33" t="n">
-        <v>6998263</v>
+        <v>6998223</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4498,11 +4478,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4511,6 +4486,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -2704,10 +2704,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122825731</v>
+        <v>122825401</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2720,31 +2720,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2753,10 +2749,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529058</v>
+        <v>529023</v>
       </c>
       <c r="R19" t="n">
-        <v>6998331</v>
+        <v>6998251</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2786,24 +2782,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2818,22 +2804,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122825401</v>
+        <v>122825731</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2846,27 +2832,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2875,10 +2865,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529023</v>
+        <v>529058</v>
       </c>
       <c r="R20" t="n">
-        <v>6998251</v>
+        <v>6998331</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2908,14 +2898,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2930,12 +2930,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -4288,10 +4288,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122825467</v>
+        <v>122826028</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4304,42 +4304,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529022</v>
+        <v>529125</v>
       </c>
       <c r="R32" t="n">
-        <v>6998263</v>
+        <v>6998223</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4371,11 +4366,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4384,6 +4374,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4400,10 +4415,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122826028</v>
+        <v>122825467</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4416,37 +4431,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529125</v>
+        <v>529022</v>
       </c>
       <c r="R33" t="n">
-        <v>6998223</v>
+        <v>6998263</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4478,6 +4498,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4486,31 +4511,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122826095</v>
+        <v>122825438</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529130</v>
+        <v>529040</v>
       </c>
       <c r="R2" t="n">
-        <v>6998225</v>
+        <v>6998249</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122825875</v>
+        <v>122826113</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529132</v>
+        <v>529119</v>
       </c>
       <c r="R3" t="n">
-        <v>6998196</v>
+        <v>6998208</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,11 +870,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -888,6 +878,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -904,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122826075</v>
+        <v>122825840</v>
       </c>
       <c r="B4" t="n">
-        <v>74847</v>
+        <v>79875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,13 +959,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529120</v>
+        <v>529095</v>
       </c>
       <c r="R4" t="n">
-        <v>6998243</v>
+        <v>6998278</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +1004,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På ved på gammal grov björkhögstubbe</t>
+          <t>På klippa i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122825635</v>
+        <v>122825991</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1052,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529077</v>
+        <v>529105</v>
       </c>
       <c r="R5" t="n">
-        <v>6998245</v>
+        <v>6998247</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,14 +1109,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1141,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122825922</v>
+        <v>122826435</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1169,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,13 +1193,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529093</v>
+        <v>529156</v>
       </c>
       <c r="R6" t="n">
-        <v>6998269</v>
+        <v>6998208</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,24 +1226,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1243,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122826113</v>
+        <v>122825432</v>
       </c>
       <c r="B7" t="n">
-        <v>79876</v>
+        <v>78502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,25 +1267,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529119</v>
+        <v>529040</v>
       </c>
       <c r="R7" t="n">
-        <v>6998208</v>
+        <v>6998249</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,11 +1328,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1336,51 +1356,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122824790</v>
+        <v>122826095</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,13 +1412,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528970</v>
+        <v>529130</v>
       </c>
       <c r="R8" t="n">
-        <v>6998415</v>
+        <v>6998225</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,11 +1445,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1463,51 +1473,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122825504</v>
+        <v>122826011</v>
       </c>
       <c r="B9" t="n">
-        <v>79875</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1516,41 +1501,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529093</v>
+        <v>529111</v>
       </c>
       <c r="R9" t="n">
-        <v>6998292</v>
+        <v>6998222</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1577,11 +1571,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1590,41 +1599,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122825531</v>
+        <v>122824605</v>
       </c>
       <c r="B10" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,31 +1627,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1666,13 +1660,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529096</v>
+        <v>528996</v>
       </c>
       <c r="R10" t="n">
-        <v>6998283</v>
+        <v>6998338</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1718,14 +1712,24 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Sten/berg på land</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stone/rock on land</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1743,10 +1747,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122825441</v>
+        <v>122824790</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,39 +1763,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529026</v>
+        <v>528970</v>
       </c>
       <c r="R11" t="n">
-        <v>6998251</v>
+        <v>6998415</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1826,11 +1825,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1839,6 +1833,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1855,7 +1874,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122825588</v>
+        <v>122825983</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1895,13 +1914,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529032</v>
+        <v>529112</v>
       </c>
       <c r="R12" t="n">
-        <v>6998357</v>
+        <v>6998258</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1928,24 +1947,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,26 +1965,51 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122824605</v>
+        <v>122825441</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1988,27 +2022,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2017,13 +2051,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528996</v>
+        <v>529026</v>
       </c>
       <c r="R13" t="n">
-        <v>6998338</v>
+        <v>6998251</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2055,6 +2089,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2063,31 +2102,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2104,10 +2118,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122825497</v>
+        <v>122824230</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2120,37 +2134,47 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529024</v>
+        <v>529044</v>
       </c>
       <c r="R14" t="n">
-        <v>6998262</v>
+        <v>6998360</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2182,6 +2206,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2190,6 +2219,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2206,10 +2260,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122824569</v>
+        <v>122825664</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2222,21 +2276,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2246,13 +2300,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528994</v>
+        <v>529058</v>
       </c>
       <c r="R15" t="n">
-        <v>6998342</v>
+        <v>6998341</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2279,14 +2333,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Lunglav på gran intill en asp med lunglav.</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,51 +2361,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122825546</v>
+        <v>122823649</v>
       </c>
       <c r="B16" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2350,41 +2389,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529031</v>
+        <v>529030</v>
       </c>
       <c r="R16" t="n">
-        <v>6998345</v>
+        <v>6998340</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2411,24 +2455,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Långväxta fertila bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2439,26 +2473,51 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122824740</v>
+        <v>122825546</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2467,25 +2526,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2495,10 +2554,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528995</v>
+        <v>529031</v>
       </c>
       <c r="R17" t="n">
-        <v>6998368</v>
+        <v>6998345</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2528,14 +2587,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2546,51 +2615,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122825432</v>
+        <v>122825531</v>
       </c>
       <c r="B18" t="n">
-        <v>78502</v>
+        <v>79876</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2599,41 +2643,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529040</v>
+        <v>529096</v>
       </c>
       <c r="R18" t="n">
-        <v>6998249</v>
+        <v>6998283</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2660,26 +2709,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2688,26 +2722,41 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122825401</v>
+        <v>122823202</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2720,39 +2769,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529023</v>
+        <v>529003</v>
       </c>
       <c r="R19" t="n">
-        <v>6998251</v>
+        <v>6998380</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2787,11 +2831,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2800,6 +2839,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2816,10 +2880,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122825731</v>
+        <v>122826075</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>74847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2828,50 +2892,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529058</v>
+        <v>529120</v>
       </c>
       <c r="R20" t="n">
-        <v>6998331</v>
+        <v>6998243</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2900,7 +2955,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2910,12 +2965,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På ved på gammal grov björkhögstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2942,10 +2997,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122826435</v>
+        <v>122825781</v>
       </c>
       <c r="B21" t="n">
-        <v>90952</v>
+        <v>95911</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2958,21 +3013,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2982,10 +3037,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529156</v>
+        <v>529100</v>
       </c>
       <c r="R21" t="n">
-        <v>6998208</v>
+        <v>6998226</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3044,10 +3099,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122825781</v>
+        <v>122825467</v>
       </c>
       <c r="B22" t="n">
-        <v>95911</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3060,34 +3115,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529100</v>
+        <v>529022</v>
       </c>
       <c r="R22" t="n">
-        <v>6998226</v>
+        <v>6998263</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3120,6 +3180,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3146,7 +3211,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122826011</v>
+        <v>122824569</v>
       </c>
       <c r="B23" t="n">
         <v>79847</v>
@@ -3179,29 +3244,20 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529111</v>
+        <v>528994</v>
       </c>
       <c r="R23" t="n">
-        <v>6998222</v>
+        <v>6998342</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3228,24 +3284,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>Lunglav på gran intill en asp med lunglav.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3256,26 +3302,51 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122824434</v>
+        <v>122825635</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3288,27 +3359,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3317,10 +3388,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529000</v>
+        <v>529077</v>
       </c>
       <c r="R24" t="n">
-        <v>6998335</v>
+        <v>6998245</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3357,7 +3428,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3368,31 +3439,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3409,10 +3455,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122826112</v>
+        <v>122826028</v>
       </c>
       <c r="B25" t="n">
-        <v>79145</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3425,21 +3471,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>257107</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3449,13 +3495,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529127</v>
+        <v>529125</v>
       </c>
       <c r="R25" t="n">
         <v>6998223</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3482,26 +3528,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3510,26 +3541,51 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122825840</v>
+        <v>122823879</v>
       </c>
       <c r="B26" t="n">
-        <v>79875</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3538,25 +3594,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3566,13 +3622,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529095</v>
+        <v>529056</v>
       </c>
       <c r="R26" t="n">
-        <v>6998278</v>
+        <v>6998335</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3599,26 +3655,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På klippa i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3627,23 +3668,48 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122823202</v>
+        <v>122825738</v>
       </c>
       <c r="B27" t="n">
         <v>78766</v>
@@ -3676,20 +3742,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529003</v>
+        <v>529116</v>
       </c>
       <c r="R27" t="n">
-        <v>6998380</v>
+        <v>6998284</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3716,11 +3791,21 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3729,51 +3814,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122823485</v>
+        <v>122825922</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3786,42 +3846,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529041</v>
+        <v>529093</v>
       </c>
       <c r="R28" t="n">
-        <v>6998374</v>
+        <v>6998269</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3848,14 +3903,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3866,51 +3931,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122825438</v>
+        <v>122823668</v>
       </c>
       <c r="B29" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3923,21 +3963,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3947,10 +3987,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529040</v>
+        <v>529038</v>
       </c>
       <c r="R29" t="n">
-        <v>6998249</v>
+        <v>6998333</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3980,26 +4020,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4008,26 +4033,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122823668</v>
+        <v>122824434</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4040,34 +4090,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529038</v>
+        <v>529000</v>
       </c>
       <c r="R30" t="n">
-        <v>6998333</v>
+        <v>6998335</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4102,6 +4157,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4118,12 +4178,12 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4133,7 +4193,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4151,10 +4211,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122823649</v>
+        <v>122825401</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4167,27 +4227,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4196,13 +4256,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529030</v>
+        <v>529023</v>
       </c>
       <c r="R31" t="n">
-        <v>6998340</v>
+        <v>6998251</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4236,7 +4296,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar.</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4247,31 +4307,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4288,10 +4323,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122826028</v>
+        <v>122823485</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4304,37 +4339,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529125</v>
+        <v>529041</v>
       </c>
       <c r="R32" t="n">
-        <v>6998223</v>
+        <v>6998374</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4366,6 +4406,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4377,27 +4422,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4415,10 +4460,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122825467</v>
+        <v>122825731</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4431,27 +4476,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4460,10 +4509,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529022</v>
+        <v>529058</v>
       </c>
       <c r="R33" t="n">
-        <v>6998263</v>
+        <v>6998331</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4493,14 +4542,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4515,19 +4574,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122823879</v>
+        <v>122824740</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4567,13 +4626,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529056</v>
+        <v>528995</v>
       </c>
       <c r="R34" t="n">
-        <v>6998335</v>
+        <v>6998368</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4605,6 +4664,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4616,7 +4680,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -4654,7 +4718,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122825738</v>
+        <v>122825395</v>
       </c>
       <c r="B35" t="n">
         <v>78766</v>
@@ -4687,29 +4751,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529116</v>
+        <v>529085</v>
       </c>
       <c r="R35" t="n">
-        <v>6998284</v>
+        <v>6998292</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4736,21 +4791,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4759,26 +4804,51 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122825395</v>
+        <v>122826112</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>79145</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4791,21 +4861,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>257107</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4815,10 +4885,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529085</v>
+        <v>529127</v>
       </c>
       <c r="R36" t="n">
-        <v>6998292</v>
+        <v>6998223</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4848,11 +4918,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4861,51 +4946,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122824230</v>
+        <v>122825588</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4918,47 +4978,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529044</v>
+        <v>529032</v>
       </c>
       <c r="R37" t="n">
-        <v>6998360</v>
+        <v>6998357</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4985,14 +5035,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5003,48 +5063,23 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122825991</v>
+        <v>122825497</v>
       </c>
       <c r="B38" t="n">
         <v>79847</v>
@@ -5084,10 +5119,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529105</v>
+        <v>529024</v>
       </c>
       <c r="R38" t="n">
-        <v>6998247</v>
+        <v>6998262</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5117,24 +5152,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5149,22 +5169,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122825983</v>
+        <v>122825504</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>79875</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5173,25 +5193,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5201,13 +5221,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529112</v>
+        <v>529093</v>
       </c>
       <c r="R39" t="n">
-        <v>6998258</v>
+        <v>6998292</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5239,11 +5259,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5258,24 +5273,14 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5293,10 +5298,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122825664</v>
+        <v>122825639</v>
       </c>
       <c r="B40" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5309,21 +5314,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5333,13 +5338,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529058</v>
+        <v>529113</v>
       </c>
       <c r="R40" t="n">
-        <v>6998341</v>
+        <v>6998294</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5366,26 +5371,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5394,26 +5384,51 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122825639</v>
+        <v>122825875</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5426,37 +5441,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529113</v>
+        <v>529132</v>
       </c>
       <c r="R41" t="n">
-        <v>6998294</v>
+        <v>6998196</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5488,6 +5508,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5496,31 +5521,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122825438</v>
+        <v>122824790</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529040</v>
+        <v>528970</v>
       </c>
       <c r="R2" t="n">
-        <v>6998249</v>
+        <v>6998415</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,26 +748,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -776,26 +761,51 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122826113</v>
+        <v>122823649</v>
       </c>
       <c r="B3" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,41 +814,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529119</v>
+        <v>529030</v>
       </c>
       <c r="R3" t="n">
-        <v>6998208</v>
+        <v>6998340</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,6 +885,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -886,12 +906,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -901,7 +921,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122825840</v>
+        <v>122826028</v>
       </c>
       <c r="B4" t="n">
-        <v>79875</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,25 +951,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,13 +979,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529095</v>
+        <v>529125</v>
       </c>
       <c r="R4" t="n">
-        <v>6998278</v>
+        <v>6998223</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,26 +1012,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På klippa i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1020,26 +1025,51 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122825991</v>
+        <v>122823485</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,37 +1082,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529105</v>
+        <v>529041</v>
       </c>
       <c r="R5" t="n">
-        <v>6998247</v>
+        <v>6998374</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,24 +1144,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,26 +1162,51 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122826435</v>
+        <v>122825497</v>
       </c>
       <c r="B6" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,21 +1219,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529156</v>
+        <v>529024</v>
       </c>
       <c r="R6" t="n">
-        <v>6998208</v>
+        <v>6998262</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122825432</v>
+        <v>122825738</v>
       </c>
       <c r="B7" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,37 +1321,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529040</v>
+        <v>529116</v>
       </c>
       <c r="R7" t="n">
-        <v>6998249</v>
+        <v>6998284</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,7 +1389,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,12 +1399,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,22 +1414,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122826095</v>
+        <v>122825588</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,21 +1442,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,13 +1466,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529130</v>
+        <v>529032</v>
       </c>
       <c r="R8" t="n">
-        <v>6998225</v>
+        <v>6998357</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,7 +1501,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1511,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,22 +1531,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122826011</v>
+        <v>122825635</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,31 +1559,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1538,13 +1588,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529111</v>
+        <v>529077</v>
       </c>
       <c r="R9" t="n">
-        <v>6998222</v>
+        <v>6998245</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1571,24 +1621,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,22 +1643,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122824605</v>
+        <v>122825441</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,27 +1671,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1660,13 +1700,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528996</v>
+        <v>529026</v>
       </c>
       <c r="R10" t="n">
-        <v>6998338</v>
+        <v>6998251</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1698,6 +1738,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1706,31 +1751,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1747,7 +1767,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122824790</v>
+        <v>122823202</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1787,10 +1807,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528970</v>
+        <v>529003</v>
       </c>
       <c r="R11" t="n">
-        <v>6998415</v>
+        <v>6998380</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1836,27 +1856,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1874,7 +1894,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122825983</v>
+        <v>122823668</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1914,13 +1934,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529112</v>
+        <v>529038</v>
       </c>
       <c r="R12" t="n">
-        <v>6998258</v>
+        <v>6998333</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1952,11 +1972,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1973,12 +1988,12 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -1988,7 +2003,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2006,10 +2021,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122825441</v>
+        <v>122825438</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2022,39 +2037,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529026</v>
+        <v>529040</v>
       </c>
       <c r="R13" t="n">
-        <v>6998251</v>
+        <v>6998249</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2084,14 +2094,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2106,22 +2126,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122824230</v>
+        <v>122825731</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2134,32 +2154,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2168,13 +2187,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529044</v>
+        <v>529058</v>
       </c>
       <c r="R14" t="n">
-        <v>6998360</v>
+        <v>6998331</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2201,14 +2220,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,51 +2248,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122825664</v>
+        <v>122825781</v>
       </c>
       <c r="B15" t="n">
-        <v>74863</v>
+        <v>95911</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2276,21 +2280,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2300,10 +2304,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529058</v>
+        <v>529100</v>
       </c>
       <c r="R15" t="n">
-        <v>6998341</v>
+        <v>6998226</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2333,24 +2337,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2365,22 +2354,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122823649</v>
+        <v>122825432</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2393,42 +2382,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529030</v>
+        <v>529040</v>
       </c>
       <c r="R16" t="n">
-        <v>6998340</v>
+        <v>6998249</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2455,14 +2439,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar.</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2473,51 +2467,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122825546</v>
+        <v>122824740</v>
       </c>
       <c r="B17" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2526,25 +2495,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2554,10 +2523,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529031</v>
+        <v>528995</v>
       </c>
       <c r="R17" t="n">
-        <v>6998345</v>
+        <v>6998368</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2587,24 +2556,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2615,26 +2574,51 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122825531</v>
+        <v>122826112</v>
       </c>
       <c r="B18" t="n">
-        <v>79876</v>
+        <v>79145</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2643,46 +2627,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>257107</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529096</v>
+        <v>529127</v>
       </c>
       <c r="R18" t="n">
-        <v>6998283</v>
+        <v>6998223</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2709,11 +2688,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2722,41 +2716,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122823202</v>
+        <v>122826075</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>74847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2765,25 +2744,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2793,13 +2772,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529003</v>
+        <v>529120</v>
       </c>
       <c r="R19" t="n">
-        <v>6998380</v>
+        <v>6998243</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2826,11 +2805,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På ved på gammal grov björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2839,51 +2833,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122826075</v>
+        <v>122824434</v>
       </c>
       <c r="B20" t="n">
-        <v>74847</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2892,41 +2861,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529120</v>
+        <v>529000</v>
       </c>
       <c r="R20" t="n">
-        <v>6998243</v>
+        <v>6998335</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2953,24 +2927,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På ved på gammal grov björkhögstubbe</t>
+          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2981,26 +2945,51 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122825781</v>
+        <v>122825664</v>
       </c>
       <c r="B21" t="n">
-        <v>95911</v>
+        <v>74863</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3013,21 +3002,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3037,10 +3026,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529100</v>
+        <v>529058</v>
       </c>
       <c r="R21" t="n">
-        <v>6998226</v>
+        <v>6998341</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3070,9 +3059,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3087,22 +3091,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122825467</v>
+        <v>122825983</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3115,42 +3119,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529022</v>
+        <v>529112</v>
       </c>
       <c r="R22" t="n">
-        <v>6998263</v>
+        <v>6998258</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3184,7 +3183,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3195,6 +3194,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3211,10 +3235,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122824569</v>
+        <v>122825531</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3223,41 +3247,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528994</v>
+        <v>529096</v>
       </c>
       <c r="R23" t="n">
-        <v>6998342</v>
+        <v>6998283</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3289,11 +3318,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Lunglav på gran intill en asp med lunglav.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3308,24 +3332,14 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3343,10 +3357,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122825635</v>
+        <v>122825395</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3359,39 +3373,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529077</v>
+        <v>529085</v>
       </c>
       <c r="R24" t="n">
-        <v>6998245</v>
+        <v>6998292</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3426,11 +3435,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3439,6 +3443,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3455,10 +3484,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122826028</v>
+        <v>122825401</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3471,37 +3500,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529125</v>
+        <v>529023</v>
       </c>
       <c r="R25" t="n">
-        <v>6998223</v>
+        <v>6998251</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3533,6 +3567,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3541,31 +3580,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3709,10 +3723,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122825738</v>
+        <v>122825875</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3725,31 +3739,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3758,13 +3768,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529116</v>
+        <v>529132</v>
       </c>
       <c r="R27" t="n">
-        <v>6998284</v>
+        <v>6998196</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3791,19 +3801,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:02</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3818,19 +3823,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122825922</v>
+        <v>122826095</v>
       </c>
       <c r="B28" t="n">
         <v>79847</v>
@@ -3870,13 +3875,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529093</v>
+        <v>529130</v>
       </c>
       <c r="R28" t="n">
-        <v>6998269</v>
+        <v>6998225</v>
       </c>
       <c r="S28" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3905,7 +3910,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3915,12 +3920,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3935,19 +3940,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122823668</v>
+        <v>122825639</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3987,13 +3992,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529038</v>
+        <v>529113</v>
       </c>
       <c r="R29" t="n">
-        <v>6998333</v>
+        <v>6998294</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4074,10 +4079,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122824434</v>
+        <v>122826113</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4086,43 +4091,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529000</v>
+        <v>529119</v>
       </c>
       <c r="R30" t="n">
-        <v>6998335</v>
+        <v>6998208</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4155,11 +4155,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4211,10 +4206,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122825401</v>
+        <v>122825991</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4227,39 +4222,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529023</v>
+        <v>529105</v>
       </c>
       <c r="R31" t="n">
-        <v>6998251</v>
+        <v>6998247</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4289,14 +4279,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4311,22 +4311,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122823485</v>
+        <v>122825840</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>79875</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4335,46 +4335,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529041</v>
+        <v>529095</v>
       </c>
       <c r="R32" t="n">
-        <v>6998374</v>
+        <v>6998278</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4401,14 +4396,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
+          <t>På klippa i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4419,51 +4424,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122825731</v>
+        <v>122824605</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4476,31 +4456,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4509,13 +4485,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529058</v>
+        <v>528996</v>
       </c>
       <c r="R33" t="n">
-        <v>6998331</v>
+        <v>6998338</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4542,26 +4518,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4570,26 +4531,51 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122824740</v>
+        <v>122825546</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4598,25 +4584,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4626,10 +4612,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528995</v>
+        <v>529031</v>
       </c>
       <c r="R34" t="n">
-        <v>6998368</v>
+        <v>6998345</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4659,14 +4645,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4677,51 +4673,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122825395</v>
+        <v>122826011</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4734,37 +4705,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529085</v>
+        <v>529111</v>
       </c>
       <c r="R35" t="n">
-        <v>6998292</v>
+        <v>6998222</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4791,11 +4771,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4804,51 +4799,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122826112</v>
+        <v>122825922</v>
       </c>
       <c r="B36" t="n">
-        <v>79145</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4861,21 +4831,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>257107</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4885,13 +4855,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529127</v>
+        <v>529093</v>
       </c>
       <c r="R36" t="n">
-        <v>6998223</v>
+        <v>6998269</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4920,7 +4890,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4930,7 +4900,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4962,10 +4932,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122825588</v>
+        <v>122825504</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>79875</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4974,25 +4944,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5002,10 +4972,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529032</v>
+        <v>529093</v>
       </c>
       <c r="R37" t="n">
-        <v>6998357</v>
+        <v>6998292</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5035,26 +5005,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5063,26 +5018,41 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122825497</v>
+        <v>122825467</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5095,34 +5065,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529024</v>
+        <v>529022</v>
       </c>
       <c r="R38" t="n">
-        <v>6998262</v>
+        <v>6998263</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5155,6 +5130,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5181,10 +5161,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122825504</v>
+        <v>122826435</v>
       </c>
       <c r="B39" t="n">
-        <v>79875</v>
+        <v>90952</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5193,25 +5173,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5221,10 +5201,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529093</v>
+        <v>529156</v>
       </c>
       <c r="R39" t="n">
-        <v>6998292</v>
+        <v>6998208</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5267,21 +5247,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5298,10 +5263,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122825639</v>
+        <v>122824569</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5314,21 +5279,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5338,10 +5303,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529113</v>
+        <v>528994</v>
       </c>
       <c r="R40" t="n">
-        <v>6998294</v>
+        <v>6998342</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -5376,6 +5341,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Lunglav på gran intill en asp med lunglav.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5392,22 +5362,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5425,7 +5395,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122825875</v>
+        <v>122824230</v>
       </c>
       <c r="B41" t="n">
         <v>57478</v>
@@ -5464,19 +5434,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529132</v>
+        <v>529044</v>
       </c>
       <c r="R41" t="n">
-        <v>6998196</v>
+        <v>6998360</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5510,7 +5485,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5521,6 +5496,31 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -2021,10 +2021,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122825438</v>
+        <v>122825731</v>
       </c>
       <c r="B13" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2037,34 +2037,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529040</v>
+        <v>529058</v>
       </c>
       <c r="R13" t="n">
-        <v>6998249</v>
+        <v>6998331</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2096,7 +2105,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2106,12 +2115,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2138,10 +2147,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122825731</v>
+        <v>122825438</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2154,43 +2163,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529058</v>
+        <v>529040</v>
       </c>
       <c r="R14" t="n">
-        <v>6998331</v>
+        <v>6998249</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -4572,10 +4572,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122825546</v>
+        <v>122826011</v>
       </c>
       <c r="B34" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4584,41 +4584,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529031</v>
+        <v>529111</v>
       </c>
       <c r="R34" t="n">
-        <v>6998345</v>
+        <v>6998222</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4647,7 +4656,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4657,12 +4666,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4677,22 +4686,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122826011</v>
+        <v>122825546</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4701,50 +4710,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529111</v>
+        <v>529031</v>
       </c>
       <c r="R35" t="n">
-        <v>6998222</v>
+        <v>6998345</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4803,12 +4803,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122824790</v>
+        <v>122824230</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528970</v>
+        <v>529044</v>
       </c>
       <c r="R2" t="n">
-        <v>6998415</v>
+        <v>6998360</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,6 +763,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -764,27 +779,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122823649</v>
+        <v>122826112</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>79148</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,42 +833,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>257107</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529030</v>
+        <v>529127</v>
       </c>
       <c r="R3" t="n">
-        <v>6998340</v>
+        <v>6998223</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,14 +890,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,51 +918,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122826028</v>
+        <v>122826075</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>74850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,25 +946,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529125</v>
+        <v>529120</v>
       </c>
       <c r="R4" t="n">
-        <v>6998223</v>
+        <v>6998243</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,11 +1007,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På ved på gammal grov björkhögstubbe</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1025,51 +1035,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122823485</v>
+        <v>122825875</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,27 +1067,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1111,13 +1096,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529041</v>
+        <v>529132</v>
       </c>
       <c r="R5" t="n">
-        <v>6998374</v>
+        <v>6998196</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1151,7 +1136,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,31 +1147,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1203,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122825497</v>
+        <v>122825664</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>74866</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1219,21 +1179,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1243,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529024</v>
+        <v>529058</v>
       </c>
       <c r="R6" t="n">
-        <v>6998262</v>
+        <v>6998341</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1276,9 +1236,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,22 +1268,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122825738</v>
+        <v>122824569</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,46 +1296,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529116</v>
+        <v>528994</v>
       </c>
       <c r="R7" t="n">
-        <v>6998284</v>
+        <v>6998342</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1387,19 +1353,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:02</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lunglav på gran intill en asp med lunglav.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,26 +1371,51 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122825588</v>
+        <v>122825991</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1442,21 +1428,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1466,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529032</v>
+        <v>529105</v>
       </c>
       <c r="R8" t="n">
-        <v>6998357</v>
+        <v>6998247</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1511,12 +1497,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1543,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122825635</v>
+        <v>122825438</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78506</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1559,39 +1545,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529077</v>
+        <v>529040</v>
       </c>
       <c r="R9" t="n">
-        <v>6998245</v>
+        <v>6998249</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1621,14 +1602,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,22 +1634,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122825441</v>
+        <v>122823879</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1671,42 +1662,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529026</v>
+        <v>529056</v>
       </c>
       <c r="R10" t="n">
-        <v>6998251</v>
+        <v>6998335</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1738,11 +1724,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1751,6 +1732,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1767,10 +1773,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122823202</v>
+        <v>122826011</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1783,37 +1789,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529003</v>
+        <v>529111</v>
       </c>
       <c r="R11" t="n">
-        <v>6998380</v>
+        <v>6998222</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1840,11 +1855,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1853,51 +1883,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122823668</v>
+        <v>122825504</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>79878</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1906,25 +1911,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1934,10 +1939,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529038</v>
+        <v>529093</v>
       </c>
       <c r="R12" t="n">
-        <v>6998333</v>
+        <v>6998292</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1986,24 +1991,14 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2021,10 +2016,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122825731</v>
+        <v>122826435</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>90955</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2037,43 +2032,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529058</v>
+        <v>529156</v>
       </c>
       <c r="R13" t="n">
-        <v>6998331</v>
+        <v>6998208</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2103,24 +2089,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2135,22 +2106,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122825438</v>
+        <v>122825588</v>
       </c>
       <c r="B14" t="n">
-        <v>78503</v>
+        <v>78769</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2163,21 +2134,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2187,10 +2158,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529040</v>
+        <v>529032</v>
       </c>
       <c r="R14" t="n">
-        <v>6998249</v>
+        <v>6998357</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2222,7 +2193,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2232,12 +2203,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2264,10 +2235,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122825781</v>
+        <v>122825840</v>
       </c>
       <c r="B15" t="n">
-        <v>95911</v>
+        <v>79878</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2276,25 +2247,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>6461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2304,10 +2275,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529100</v>
+        <v>529095</v>
       </c>
       <c r="R15" t="n">
-        <v>6998226</v>
+        <v>6998278</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2337,9 +2308,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På klippa i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2354,22 +2340,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122825432</v>
+        <v>122824790</v>
       </c>
       <c r="B16" t="n">
-        <v>78502</v>
+        <v>78769</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2382,21 +2368,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2406,10 +2392,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529040</v>
+        <v>528970</v>
       </c>
       <c r="R16" t="n">
-        <v>6998249</v>
+        <v>6998415</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2439,26 +2425,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2467,26 +2438,51 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122824740</v>
+        <v>122825639</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2523,13 +2519,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528995</v>
+        <v>529113</v>
       </c>
       <c r="R17" t="n">
-        <v>6998368</v>
+        <v>6998294</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2561,11 +2557,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2582,22 +2573,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2615,10 +2606,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122826112</v>
+        <v>122825546</v>
       </c>
       <c r="B18" t="n">
-        <v>79145</v>
+        <v>79754</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2627,25 +2618,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>257107</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2655,10 +2646,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529127</v>
+        <v>529031</v>
       </c>
       <c r="R18" t="n">
-        <v>6998223</v>
+        <v>6998345</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2690,7 +2681,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2700,7 +2691,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2732,10 +2723,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122826075</v>
+        <v>122825432</v>
       </c>
       <c r="B19" t="n">
-        <v>74847</v>
+        <v>78505</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2744,25 +2735,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6439</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2772,13 +2763,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529120</v>
+        <v>529040</v>
       </c>
       <c r="R19" t="n">
-        <v>6998243</v>
+        <v>6998249</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2807,7 +2798,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2817,12 +2808,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På ved på gammal grov björkhögstubbe</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2849,10 +2840,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122824434</v>
+        <v>122823485</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2865,21 +2856,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2894,13 +2885,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529000</v>
+        <v>529041</v>
       </c>
       <c r="R20" t="n">
-        <v>6998335</v>
+        <v>6998374</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2934,7 +2925,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
+          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2948,27 +2939,27 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2986,10 +2977,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122825664</v>
+        <v>122825467</v>
       </c>
       <c r="B21" t="n">
-        <v>74863</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3002,34 +2993,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529058</v>
+        <v>529022</v>
       </c>
       <c r="R21" t="n">
-        <v>6998341</v>
+        <v>6998263</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3059,24 +3055,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3091,22 +3077,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122825983</v>
+        <v>122823202</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3143,13 +3129,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529112</v>
+        <v>529003</v>
       </c>
       <c r="R22" t="n">
-        <v>6998258</v>
+        <v>6998380</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3181,11 +3167,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3197,27 +3178,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3235,10 +3216,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122825531</v>
+        <v>122826095</v>
       </c>
       <c r="B23" t="n">
-        <v>79876</v>
+        <v>79850</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3247,46 +3228,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529096</v>
+        <v>529130</v>
       </c>
       <c r="R23" t="n">
-        <v>6998283</v>
+        <v>6998225</v>
       </c>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3313,11 +3289,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3326,41 +3317,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122825395</v>
+        <v>122823668</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3397,10 +3373,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529085</v>
+        <v>529038</v>
       </c>
       <c r="R24" t="n">
-        <v>6998292</v>
+        <v>6998333</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3451,22 +3427,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3484,10 +3460,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122825401</v>
+        <v>122824605</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3500,27 +3476,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3529,13 +3505,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529023</v>
+        <v>528996</v>
       </c>
       <c r="R25" t="n">
-        <v>6998251</v>
+        <v>6998338</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3567,11 +3543,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3580,6 +3551,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3596,10 +3592,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122823879</v>
+        <v>122825531</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>79879</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3608,41 +3604,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529056</v>
+        <v>529096</v>
       </c>
       <c r="R26" t="n">
-        <v>6998335</v>
+        <v>6998283</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3685,27 +3686,17 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3723,10 +3714,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122825875</v>
+        <v>122825635</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3768,10 +3759,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529132</v>
+        <v>529077</v>
       </c>
       <c r="R27" t="n">
-        <v>6998196</v>
+        <v>6998245</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3808,7 +3799,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3835,10 +3826,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122826095</v>
+        <v>122825781</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>95914</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3851,21 +3842,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3875,13 +3866,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529130</v>
+        <v>529100</v>
       </c>
       <c r="R28" t="n">
-        <v>6998225</v>
+        <v>6998226</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3908,24 +3899,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3940,22 +3916,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122825639</v>
+        <v>122825922</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3968,21 +3944,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3992,13 +3968,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529113</v>
+        <v>529093</v>
       </c>
       <c r="R29" t="n">
-        <v>6998294</v>
+        <v>6998269</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4025,11 +4001,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4038,51 +4029,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122826113</v>
+        <v>122825731</v>
       </c>
       <c r="B30" t="n">
-        <v>79876</v>
+        <v>78769</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4091,38 +4057,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529119</v>
+        <v>529058</v>
       </c>
       <c r="R30" t="n">
-        <v>6998208</v>
+        <v>6998331</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4152,11 +4127,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4165,51 +4155,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122825991</v>
+        <v>122823649</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4222,37 +4187,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529105</v>
+        <v>529030</v>
       </c>
       <c r="R31" t="n">
-        <v>6998247</v>
+        <v>6998340</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4279,24 +4249,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Långväxta fertila bålar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4307,26 +4267,51 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122825840</v>
+        <v>122826113</v>
       </c>
       <c r="B32" t="n">
-        <v>79875</v>
+        <v>79879</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4339,21 +4324,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4363,10 +4348,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529095</v>
+        <v>529119</v>
       </c>
       <c r="R32" t="n">
-        <v>6998278</v>
+        <v>6998208</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4396,26 +4381,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På klippa i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4424,26 +4394,51 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122824605</v>
+        <v>122825738</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4456,27 +4451,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4485,13 +4484,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528996</v>
+        <v>529116</v>
       </c>
       <c r="R33" t="n">
-        <v>6998338</v>
+        <v>6998284</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4518,11 +4517,21 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4531,51 +4540,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122826011</v>
+        <v>122825497</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4605,29 +4589,20 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529111</v>
+        <v>529024</v>
       </c>
       <c r="R34" t="n">
-        <v>6998222</v>
+        <v>6998262</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4654,24 +4629,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4686,22 +4646,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122825546</v>
+        <v>122826028</v>
       </c>
       <c r="B35" t="n">
-        <v>79751</v>
+        <v>79850</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4710,25 +4670,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4738,13 +4698,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529031</v>
+        <v>529125</v>
       </c>
       <c r="R35" t="n">
-        <v>6998345</v>
+        <v>6998223</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4771,26 +4731,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4799,26 +4744,51 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122825922</v>
+        <v>122825441</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4831,37 +4801,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529093</v>
+        <v>529026</v>
       </c>
       <c r="R36" t="n">
-        <v>6998269</v>
+        <v>6998251</v>
       </c>
       <c r="S36" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4888,24 +4863,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4920,22 +4885,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122825504</v>
+        <v>122825983</v>
       </c>
       <c r="B37" t="n">
-        <v>79875</v>
+        <v>78769</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4944,25 +4909,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4972,13 +4937,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529093</v>
+        <v>529112</v>
       </c>
       <c r="R37" t="n">
-        <v>6998292</v>
+        <v>6998258</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5010,6 +4975,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5024,14 +4994,24 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Sten/berg på land</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stone/rock on land</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5049,10 +5029,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122825467</v>
+        <v>122825395</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5065,39 +5045,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529022</v>
+        <v>529085</v>
       </c>
       <c r="R38" t="n">
-        <v>6998263</v>
+        <v>6998292</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5132,11 +5107,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5145,6 +5115,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5161,10 +5156,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122826435</v>
+        <v>122824740</v>
       </c>
       <c r="B39" t="n">
-        <v>90952</v>
+        <v>78769</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5177,21 +5172,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5201,10 +5196,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529156</v>
+        <v>528995</v>
       </c>
       <c r="R39" t="n">
-        <v>6998208</v>
+        <v>6998368</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5239,6 +5234,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5247,6 +5247,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5263,10 +5288,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122824569</v>
+        <v>122825401</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5279,37 +5304,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528994</v>
+        <v>529023</v>
       </c>
       <c r="R40" t="n">
-        <v>6998342</v>
+        <v>6998251</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5343,7 +5373,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Lunglav på gran intill en asp med lunglav.</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5354,31 +5384,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5395,10 +5400,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122824230</v>
+        <v>122824434</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5411,32 +5416,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5445,13 +5445,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529044</v>
+        <v>529000</v>
       </c>
       <c r="R41" t="n">
-        <v>6998360</v>
+        <v>6998335</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
+          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5499,27 +5499,27 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122824230</v>
+        <v>122825922</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,47 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529044</v>
+        <v>529093</v>
       </c>
       <c r="R2" t="n">
-        <v>6998360</v>
+        <v>6998269</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,14 +748,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,51 +776,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122826112</v>
+        <v>122826113</v>
       </c>
       <c r="B3" t="n">
-        <v>79148</v>
+        <v>79881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>257107</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -857,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529127</v>
+        <v>529119</v>
       </c>
       <c r="R3" t="n">
-        <v>6998223</v>
+        <v>6998208</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,26 +865,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -918,26 +878,51 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122826075</v>
+        <v>122825635</v>
       </c>
       <c r="B4" t="n">
-        <v>74850</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,41 +931,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529120</v>
+        <v>529077</v>
       </c>
       <c r="R4" t="n">
-        <v>6998243</v>
+        <v>6998245</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,24 +997,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På ved på gammal grov björkhögstubbe</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122825875</v>
+        <v>122825546</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>79756</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,43 +1043,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529132</v>
+        <v>529031</v>
       </c>
       <c r="R5" t="n">
-        <v>6998196</v>
+        <v>6998345</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,14 +1104,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,22 +1136,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122825664</v>
+        <v>122823202</v>
       </c>
       <c r="B6" t="n">
-        <v>74866</v>
+        <v>78771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,21 +1164,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529058</v>
+        <v>529003</v>
       </c>
       <c r="R6" t="n">
-        <v>6998341</v>
+        <v>6998380</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,26 +1221,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1264,26 +1234,51 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122824569</v>
+        <v>122824434</v>
       </c>
       <c r="B7" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1314,19 +1309,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528994</v>
+        <v>529000</v>
       </c>
       <c r="R7" t="n">
-        <v>6998342</v>
+        <v>6998335</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Lunglav på gran intill en asp med lunglav.</t>
+          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,22 +1379,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122825991</v>
+        <v>122824569</v>
       </c>
       <c r="B8" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529105</v>
+        <v>528994</v>
       </c>
       <c r="R8" t="n">
-        <v>6998247</v>
+        <v>6998342</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1485,24 +1485,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Lunglav på gran intill en asp med lunglav.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,26 +1503,51 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122825438</v>
+        <v>122825588</v>
       </c>
       <c r="B9" t="n">
-        <v>78506</v>
+        <v>78771</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1545,21 +1560,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1569,10 +1584,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529040</v>
+        <v>529032</v>
       </c>
       <c r="R9" t="n">
-        <v>6998249</v>
+        <v>6998357</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1604,7 +1619,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1614,12 +1629,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1646,10 +1661,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122823879</v>
+        <v>122825441</v>
       </c>
       <c r="B10" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1662,37 +1677,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529056</v>
+        <v>529026</v>
       </c>
       <c r="R10" t="n">
-        <v>6998335</v>
+        <v>6998251</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1724,6 +1744,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1732,31 +1757,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1773,10 +1773,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122826011</v>
+        <v>122825664</v>
       </c>
       <c r="B11" t="n">
-        <v>79850</v>
+        <v>74866</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1789,46 +1789,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529111</v>
+        <v>529058</v>
       </c>
       <c r="R11" t="n">
-        <v>6998222</v>
+        <v>6998341</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1857,7 +1848,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1867,12 +1858,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,22 +1878,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122825504</v>
+        <v>122825497</v>
       </c>
       <c r="B12" t="n">
-        <v>79878</v>
+        <v>79852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,25 +1902,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1939,10 +1930,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529093</v>
+        <v>529024</v>
       </c>
       <c r="R12" t="n">
-        <v>6998292</v>
+        <v>6998262</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1985,21 +1976,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2016,10 +1992,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122826435</v>
+        <v>122824230</v>
       </c>
       <c r="B13" t="n">
-        <v>90955</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2032,37 +2008,47 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529156</v>
+        <v>529044</v>
       </c>
       <c r="R13" t="n">
-        <v>6998208</v>
+        <v>6998360</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2094,6 +2080,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2102,6 +2093,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2118,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122825588</v>
+        <v>122824790</v>
       </c>
       <c r="B14" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2158,10 +2174,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529032</v>
+        <v>528970</v>
       </c>
       <c r="R14" t="n">
-        <v>6998357</v>
+        <v>6998415</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2191,26 +2207,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2219,26 +2220,51 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122825840</v>
+        <v>122823879</v>
       </c>
       <c r="B15" t="n">
-        <v>79878</v>
+        <v>78771</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2247,25 +2273,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2275,13 +2301,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529095</v>
+        <v>529056</v>
       </c>
       <c r="R15" t="n">
-        <v>6998278</v>
+        <v>6998335</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2308,26 +2334,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På klippa i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2336,26 +2347,51 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122824790</v>
+        <v>122826095</v>
       </c>
       <c r="B16" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2368,21 +2404,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2392,13 +2428,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528970</v>
+        <v>529130</v>
       </c>
       <c r="R16" t="n">
-        <v>6998415</v>
+        <v>6998225</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2425,11 +2461,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2438,51 +2489,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122825639</v>
+        <v>122826112</v>
       </c>
       <c r="B17" t="n">
-        <v>78769</v>
+        <v>79150</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2495,21 +2521,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>257107</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2519,13 +2545,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529113</v>
+        <v>529127</v>
       </c>
       <c r="R17" t="n">
-        <v>6998294</v>
+        <v>6998223</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2552,11 +2578,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2565,51 +2606,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122825546</v>
+        <v>122825781</v>
       </c>
       <c r="B18" t="n">
-        <v>79754</v>
+        <v>95916</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2618,25 +2634,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2646,10 +2662,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529031</v>
+        <v>529100</v>
       </c>
       <c r="R18" t="n">
-        <v>6998345</v>
+        <v>6998226</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2679,24 +2695,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2711,22 +2712,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122825432</v>
+        <v>122826011</v>
       </c>
       <c r="B19" t="n">
-        <v>78505</v>
+        <v>79852</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,37 +2740,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529040</v>
+        <v>529111</v>
       </c>
       <c r="R19" t="n">
-        <v>6998249</v>
+        <v>6998222</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2798,7 +2808,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2808,12 +2818,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2828,22 +2838,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122823485</v>
+        <v>122825467</v>
       </c>
       <c r="B20" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2856,27 +2866,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2885,13 +2895,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529041</v>
+        <v>529022</v>
       </c>
       <c r="R20" t="n">
-        <v>6998374</v>
+        <v>6998263</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2925,7 +2935,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2936,31 +2946,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2977,10 +2962,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122825467</v>
+        <v>122826075</v>
       </c>
       <c r="B21" t="n">
-        <v>57481</v>
+        <v>74850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2989,46 +2974,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529022</v>
+        <v>529120</v>
       </c>
       <c r="R21" t="n">
-        <v>6998263</v>
+        <v>6998243</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3055,14 +3035,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På ved på gammal grov björkhögstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3077,22 +3067,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122823202</v>
+        <v>122825991</v>
       </c>
       <c r="B22" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3105,21 +3095,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3129,10 +3119,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529003</v>
+        <v>529105</v>
       </c>
       <c r="R22" t="n">
-        <v>6998380</v>
+        <v>6998247</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3162,11 +3152,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3175,51 +3180,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122826095</v>
+        <v>122825401</v>
       </c>
       <c r="B23" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3232,37 +3212,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529130</v>
+        <v>529023</v>
       </c>
       <c r="R23" t="n">
-        <v>6998225</v>
+        <v>6998251</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3289,24 +3274,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3321,22 +3296,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122823668</v>
+        <v>122825432</v>
       </c>
       <c r="B24" t="n">
-        <v>78769</v>
+        <v>78507</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3349,21 +3324,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3373,10 +3348,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529038</v>
+        <v>529040</v>
       </c>
       <c r="R24" t="n">
-        <v>6998333</v>
+        <v>6998249</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3406,11 +3381,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3419,51 +3409,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122824605</v>
+        <v>122825731</v>
       </c>
       <c r="B25" t="n">
-        <v>79850</v>
+        <v>78771</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3476,27 +3441,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3505,13 +3474,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528996</v>
+        <v>529058</v>
       </c>
       <c r="R25" t="n">
-        <v>6998338</v>
+        <v>6998331</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3538,11 +3507,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3551,51 +3535,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122825531</v>
+        <v>122825738</v>
       </c>
       <c r="B26" t="n">
-        <v>79879</v>
+        <v>78771</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3604,31 +3563,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3637,13 +3600,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529096</v>
+        <v>529116</v>
       </c>
       <c r="R26" t="n">
-        <v>6998283</v>
+        <v>6998284</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3670,11 +3633,21 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3683,41 +3656,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122825635</v>
+        <v>122823668</v>
       </c>
       <c r="B27" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3730,39 +3688,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529077</v>
+        <v>529038</v>
       </c>
       <c r="R27" t="n">
-        <v>6998245</v>
+        <v>6998333</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3797,11 +3750,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3810,6 +3758,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3826,10 +3799,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122825781</v>
+        <v>122824605</v>
       </c>
       <c r="B28" t="n">
-        <v>95914</v>
+        <v>79852</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3842,37 +3815,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529100</v>
+        <v>528996</v>
       </c>
       <c r="R28" t="n">
-        <v>6998226</v>
+        <v>6998338</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3912,6 +3890,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3928,10 +3931,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122825922</v>
+        <v>122825438</v>
       </c>
       <c r="B29" t="n">
-        <v>79850</v>
+        <v>78508</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3944,21 +3947,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3968,13 +3971,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529093</v>
+        <v>529040</v>
       </c>
       <c r="R29" t="n">
-        <v>6998269</v>
+        <v>6998249</v>
       </c>
       <c r="S29" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4003,7 +4006,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4013,12 +4016,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4045,10 +4048,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122825731</v>
+        <v>122825504</v>
       </c>
       <c r="B30" t="n">
-        <v>78769</v>
+        <v>79880</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4057,47 +4060,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529058</v>
+        <v>529093</v>
       </c>
       <c r="R30" t="n">
-        <v>6998331</v>
+        <v>6998292</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4127,26 +4121,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4155,26 +4134,41 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122823649</v>
+        <v>122825531</v>
       </c>
       <c r="B31" t="n">
-        <v>78769</v>
+        <v>79881</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4183,25 +4177,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4216,13 +4210,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529030</v>
+        <v>529096</v>
       </c>
       <c r="R31" t="n">
-        <v>6998340</v>
+        <v>6998283</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4254,11 +4248,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Långväxta fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4273,24 +4262,14 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4308,10 +4287,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122826113</v>
+        <v>122825395</v>
       </c>
       <c r="B32" t="n">
-        <v>79879</v>
+        <v>78771</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4320,25 +4299,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4348,10 +4327,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529119</v>
+        <v>529085</v>
       </c>
       <c r="R32" t="n">
-        <v>6998208</v>
+        <v>6998292</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4402,22 +4381,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4435,10 +4414,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122825738</v>
+        <v>122825875</v>
       </c>
       <c r="B33" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4451,31 +4430,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4484,13 +4459,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529116</v>
+        <v>529132</v>
       </c>
       <c r="R33" t="n">
-        <v>6998284</v>
+        <v>6998196</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4517,19 +4492,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:02</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4544,22 +4514,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122825497</v>
+        <v>122825840</v>
       </c>
       <c r="B34" t="n">
-        <v>79850</v>
+        <v>79880</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4568,25 +4538,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4596,10 +4566,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529024</v>
+        <v>529095</v>
       </c>
       <c r="R34" t="n">
-        <v>6998262</v>
+        <v>6998278</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4629,9 +4599,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På klippa i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4646,22 +4631,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122826028</v>
+        <v>122826435</v>
       </c>
       <c r="B35" t="n">
-        <v>79850</v>
+        <v>90957</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4674,21 +4659,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4698,13 +4683,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529125</v>
+        <v>529156</v>
       </c>
       <c r="R35" t="n">
-        <v>6998223</v>
+        <v>6998208</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4744,31 +4729,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4785,10 +4745,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122825441</v>
+        <v>122823485</v>
       </c>
       <c r="B36" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4801,27 +4761,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4830,13 +4790,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529026</v>
+        <v>529041</v>
       </c>
       <c r="R36" t="n">
-        <v>6998251</v>
+        <v>6998374</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4870,7 +4830,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4881,6 +4841,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4900,7 +4885,7 @@
         <v>122825983</v>
       </c>
       <c r="B37" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5029,10 +5014,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122825395</v>
+        <v>122825639</v>
       </c>
       <c r="B38" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5069,13 +5054,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529085</v>
+        <v>529113</v>
       </c>
       <c r="R38" t="n">
-        <v>6998292</v>
+        <v>6998294</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5123,22 +5108,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5156,10 +5141,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122824740</v>
+        <v>122823649</v>
       </c>
       <c r="B39" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5190,19 +5175,24 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528995</v>
+        <v>529030</v>
       </c>
       <c r="R39" t="n">
-        <v>6998368</v>
+        <v>6998340</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5236,7 +5226,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Långväxta fertila bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5255,22 +5245,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5288,10 +5278,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122825401</v>
+        <v>122826028</v>
       </c>
       <c r="B40" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5304,42 +5294,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529023</v>
+        <v>529125</v>
       </c>
       <c r="R40" t="n">
-        <v>6998251</v>
+        <v>6998223</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5371,11 +5356,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5384,6 +5364,31 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5400,10 +5405,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122824434</v>
+        <v>122824740</v>
       </c>
       <c r="B41" t="n">
-        <v>79850</v>
+        <v>78771</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5416,39 +5421,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529000</v>
+        <v>528995</v>
       </c>
       <c r="R41" t="n">
-        <v>6998335</v>
+        <v>6998368</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5504,22 +5504,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122825922</v>
+        <v>122825635</v>
       </c>
       <c r="B2" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529093</v>
+        <v>529077</v>
       </c>
       <c r="R2" t="n">
-        <v>6998269</v>
+        <v>6998245</v>
       </c>
       <c r="S2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,24 +753,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122826113</v>
+        <v>122825922</v>
       </c>
       <c r="B3" t="n">
-        <v>79881</v>
+        <v>79852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529119</v>
+        <v>529093</v>
       </c>
       <c r="R3" t="n">
-        <v>6998208</v>
+        <v>6998269</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,11 +860,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -878,51 +888,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122825635</v>
+        <v>122826113</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>79881</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,43 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529077</v>
+        <v>529119</v>
       </c>
       <c r="R4" t="n">
-        <v>6998245</v>
+        <v>6998208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,11 +982,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack tall</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1015,6 +990,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -2505,10 +2505,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122826112</v>
+        <v>122825781</v>
       </c>
       <c r="B17" t="n">
-        <v>79150</v>
+        <v>95916</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2521,21 +2521,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>257107</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529127</v>
+        <v>529100</v>
       </c>
       <c r="R17" t="n">
-        <v>6998223</v>
+        <v>6998226</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2578,24 +2578,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2610,22 +2595,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122825781</v>
+        <v>122826011</v>
       </c>
       <c r="B18" t="n">
-        <v>95916</v>
+        <v>79852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2638,37 +2623,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529100</v>
+        <v>529111</v>
       </c>
       <c r="R18" t="n">
-        <v>6998226</v>
+        <v>6998222</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2695,9 +2689,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2712,22 +2721,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122826011</v>
+        <v>122826112</v>
       </c>
       <c r="B19" t="n">
-        <v>79852</v>
+        <v>79150</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2740,46 +2749,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>257107</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>S.Ekman</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529111</v>
+        <v>529127</v>
       </c>
       <c r="R19" t="n">
-        <v>6998222</v>
+        <v>6998223</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal asp</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2838,12 +2838,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122825395</v>
+        <v>122825875</v>
       </c>
       <c r="B32" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4303,34 +4303,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529085</v>
+        <v>529132</v>
       </c>
       <c r="R32" t="n">
-        <v>6998292</v>
+        <v>6998196</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4365,6 +4370,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4373,31 +4383,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4414,10 +4399,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122825875</v>
+        <v>122825395</v>
       </c>
       <c r="B33" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4430,39 +4415,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529132</v>
+        <v>529085</v>
       </c>
       <c r="R33" t="n">
-        <v>6998196</v>
+        <v>6998292</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4497,11 +4477,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4510,6 +4485,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">

--- a/artfynd/A 55404-2024 artfynd.xlsx
+++ b/artfynd/A 55404-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122825922</v>
+        <v>122826435</v>
       </c>
       <c r="B3" t="n">
-        <v>79852</v>
+        <v>90963</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529093</v>
+        <v>529156</v>
       </c>
       <c r="R3" t="n">
-        <v>6998269</v>
+        <v>6998208</v>
       </c>
       <c r="S3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,24 +860,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122826113</v>
+        <v>122825875</v>
       </c>
       <c r="B4" t="n">
-        <v>79881</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +901,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529119</v>
+        <v>529132</v>
       </c>
       <c r="R4" t="n">
-        <v>6998208</v>
+        <v>6998196</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,6 +972,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -990,31 +985,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1031,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122825546</v>
+        <v>122825639</v>
       </c>
       <c r="B5" t="n">
-        <v>79756</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,13 +1041,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529031</v>
+        <v>529113</v>
       </c>
       <c r="R5" t="n">
-        <v>6998345</v>
+        <v>6998294</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,26 +1074,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1132,26 +1087,51 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122823202</v>
+        <v>122824569</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,13 +1168,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529003</v>
+        <v>528994</v>
       </c>
       <c r="R6" t="n">
-        <v>6998380</v>
+        <v>6998342</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,6 +1206,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lunglav på gran intill en asp med lunglav.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1237,7 +1222,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1275,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122824434</v>
+        <v>122825664</v>
       </c>
       <c r="B7" t="n">
-        <v>79852</v>
+        <v>74866</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,39 +1276,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529000</v>
+        <v>529058</v>
       </c>
       <c r="R7" t="n">
-        <v>6998335</v>
+        <v>6998341</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,14 +1333,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,51 +1361,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122824569</v>
+        <v>122825731</v>
       </c>
       <c r="B8" t="n">
-        <v>79852</v>
+        <v>78772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,37 +1393,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528994</v>
+        <v>529058</v>
       </c>
       <c r="R8" t="n">
-        <v>6998342</v>
+        <v>6998331</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1485,14 +1459,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Lunglav på gran intill en asp med lunglav.</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,51 +1487,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122825588</v>
+        <v>122826112</v>
       </c>
       <c r="B9" t="n">
-        <v>78771</v>
+        <v>79151</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,21 +1519,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>257107</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blek lundlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bacidia rosellizans</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>S.Ekman</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1584,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529032</v>
+        <v>529127</v>
       </c>
       <c r="R9" t="n">
-        <v>6998357</v>
+        <v>6998223</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1619,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1629,12 +1588,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1661,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122825441</v>
+        <v>122825983</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1677,42 +1636,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529026</v>
+        <v>529112</v>
       </c>
       <c r="R10" t="n">
-        <v>6998251</v>
+        <v>6998258</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1746,7 +1700,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1757,6 +1711,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1773,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122825664</v>
+        <v>122824790</v>
       </c>
       <c r="B11" t="n">
-        <v>74866</v>
+        <v>78772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1789,21 +1768,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1813,10 +1792,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529058</v>
+        <v>528970</v>
       </c>
       <c r="R11" t="n">
-        <v>6998341</v>
+        <v>6998415</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1846,26 +1825,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1874,26 +1838,51 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122825497</v>
+        <v>122824434</v>
       </c>
       <c r="B12" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1924,16 +1913,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529024</v>
+        <v>529000</v>
       </c>
       <c r="R12" t="n">
-        <v>6998262</v>
+        <v>6998335</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1968,6 +1962,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fertil lunglav på asp med gott om yngre bålar.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1976,6 +1975,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1992,10 +2016,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122824230</v>
+        <v>122824740</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2008,47 +2032,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529044</v>
+        <v>528995</v>
       </c>
       <c r="R13" t="n">
-        <v>6998360</v>
+        <v>6998368</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2082,7 +2096,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,7 +2110,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2111,12 +2125,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2134,10 +2148,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122824790</v>
+        <v>122824605</v>
       </c>
       <c r="B14" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2150,37 +2164,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528970</v>
+        <v>528996</v>
       </c>
       <c r="R14" t="n">
-        <v>6998415</v>
+        <v>6998338</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2228,12 +2247,12 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2243,7 +2262,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2261,10 +2280,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122823879</v>
+        <v>122823649</v>
       </c>
       <c r="B15" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2295,19 +2314,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529056</v>
+        <v>529030</v>
       </c>
       <c r="R15" t="n">
-        <v>6998335</v>
+        <v>6998340</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2339,6 +2363,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Långväxta fertila bålar.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2350,27 +2379,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2388,10 +2417,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122826095</v>
+        <v>122825395</v>
       </c>
       <c r="B16" t="n">
-        <v>79852</v>
+        <v>78772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2404,21 +2433,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2428,13 +2457,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529130</v>
+        <v>529085</v>
       </c>
       <c r="R16" t="n">
-        <v>6998225</v>
+        <v>6998292</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2461,26 +2490,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2489,26 +2503,51 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122825781</v>
+        <v>122823879</v>
       </c>
       <c r="B17" t="n">
-        <v>95916</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2521,21 +2560,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2545,13 +2584,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529100</v>
+        <v>529056</v>
       </c>
       <c r="R17" t="n">
-        <v>6998226</v>
+        <v>6998335</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2591,6 +2630,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2607,10 +2671,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122826011</v>
+        <v>122825781</v>
       </c>
       <c r="B18" t="n">
-        <v>79852</v>
+        <v>95922</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2623,46 +2687,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529111</v>
+        <v>529100</v>
       </c>
       <c r="R18" t="n">
-        <v>6998222</v>
+        <v>6998226</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2689,24 +2744,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2721,22 +2761,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122826112</v>
+        <v>122825432</v>
       </c>
       <c r="B19" t="n">
-        <v>79150</v>
+        <v>78508</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2749,21 +2789,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>257107</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blek lundlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bacidia rosellizans</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>S.Ekman</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2773,10 +2813,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529127</v>
+        <v>529040</v>
       </c>
       <c r="R19" t="n">
-        <v>6998223</v>
+        <v>6998249</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2808,7 +2848,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2818,12 +2858,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2850,10 +2890,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122825467</v>
+        <v>122825840</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
+        <v>79881</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2862,43 +2902,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529022</v>
+        <v>529095</v>
       </c>
       <c r="R20" t="n">
-        <v>6998263</v>
+        <v>6998278</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2928,14 +2963,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På klippa i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2950,22 +2995,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122826075</v>
+        <v>122825441</v>
       </c>
       <c r="B21" t="n">
-        <v>74850</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2974,41 +3019,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6439</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529120</v>
+        <v>529026</v>
       </c>
       <c r="R21" t="n">
-        <v>6998243</v>
+        <v>6998251</v>
       </c>
       <c r="S21" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3035,24 +3085,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På ved på gammal grov björkhögstubbe</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3067,22 +3107,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122825991</v>
+        <v>122826075</v>
       </c>
       <c r="B22" t="n">
-        <v>79852</v>
+        <v>74850</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3091,25 +3131,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3119,13 +3159,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529105</v>
+        <v>529120</v>
       </c>
       <c r="R22" t="n">
-        <v>6998247</v>
+        <v>6998243</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3154,7 +3194,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3164,12 +3204,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
+          <t>På ved på gammal grov björkhögstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3196,7 +3236,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122825401</v>
+        <v>122824230</v>
       </c>
       <c r="B23" t="n">
         <v>57481</v>
@@ -3232,7 +3272,12 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3241,13 +3286,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529023</v>
+        <v>529044</v>
       </c>
       <c r="R23" t="n">
-        <v>6998251</v>
+        <v>6998360</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3281,7 +3326,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack tall</t>
+          <t>Äldre ringhack på en numera död stående  gran med full längd.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3292,6 +3337,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3308,10 +3378,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122825432</v>
+        <v>122825922</v>
       </c>
       <c r="B24" t="n">
-        <v>78507</v>
+        <v>79853</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3324,21 +3394,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3348,13 +3418,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529040</v>
+        <v>529093</v>
       </c>
       <c r="R24" t="n">
-        <v>6998249</v>
+        <v>6998269</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3383,7 +3453,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3393,12 +3463,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3425,10 +3495,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122825731</v>
+        <v>122826095</v>
       </c>
       <c r="B25" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3441,46 +3511,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529058</v>
+        <v>529130</v>
       </c>
       <c r="R25" t="n">
-        <v>6998331</v>
+        <v>6998225</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3509,7 +3570,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3519,12 +3580,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3539,22 +3600,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122825738</v>
+        <v>122826028</v>
       </c>
       <c r="B26" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3567,46 +3628,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529116</v>
+        <v>529125</v>
       </c>
       <c r="R26" t="n">
-        <v>6998284</v>
+        <v>6998223</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3633,21 +3685,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3656,16 +3698,41 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3675,7 +3742,7 @@
         <v>122823668</v>
       </c>
       <c r="B27" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3799,10 +3866,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122824605</v>
+        <v>122825497</v>
       </c>
       <c r="B28" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3833,24 +3900,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528996</v>
+        <v>529024</v>
       </c>
       <c r="R28" t="n">
-        <v>6998338</v>
+        <v>6998262</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3890,31 +3952,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3931,10 +3968,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122825438</v>
+        <v>122825991</v>
       </c>
       <c r="B29" t="n">
-        <v>78508</v>
+        <v>79853</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3947,21 +3984,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3971,10 +4008,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529040</v>
+        <v>529105</v>
       </c>
       <c r="R29" t="n">
-        <v>6998249</v>
+        <v>6998247</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4006,7 +4043,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4016,12 +4053,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4048,10 +4085,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122825504</v>
+        <v>122825738</v>
       </c>
       <c r="B30" t="n">
-        <v>79880</v>
+        <v>78772</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4060,41 +4097,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529093</v>
+        <v>529116</v>
       </c>
       <c r="R30" t="n">
-        <v>6998292</v>
+        <v>6998284</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4121,11 +4167,21 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4134,41 +4190,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122825531</v>
+        <v>122825588</v>
       </c>
       <c r="B31" t="n">
-        <v>79881</v>
+        <v>78772</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4177,46 +4218,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529096</v>
+        <v>529032</v>
       </c>
       <c r="R31" t="n">
-        <v>6998283</v>
+        <v>6998357</v>
       </c>
       <c r="S31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4243,11 +4279,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4256,38 +4307,23 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Sten/berg på land</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stone/rock on land</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122825875</v>
+        <v>122825401</v>
       </c>
       <c r="B32" t="n">
         <v>57481</v>
@@ -4323,7 +4359,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4332,10 +4368,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529132</v>
+        <v>529023</v>
       </c>
       <c r="R32" t="n">
-        <v>6998196</v>
+        <v>6998251</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4372,7 +4408,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4399,10 +4435,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122825395</v>
+        <v>122825467</v>
       </c>
       <c r="B33" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4415,34 +4451,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529085</v>
+        <v>529022</v>
       </c>
       <c r="R33" t="n">
-        <v>6998292</v>
+        <v>6998263</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4477,6 +4518,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4485,31 +4531,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4526,10 +4547,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122825840</v>
+        <v>122826113</v>
       </c>
       <c r="B34" t="n">
-        <v>79880</v>
+        <v>79882</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4542,21 +4563,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4566,10 +4587,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529095</v>
+        <v>529119</v>
       </c>
       <c r="R34" t="n">
-        <v>6998278</v>
+        <v>6998208</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4599,26 +4620,11 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På klippa i gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4627,26 +4633,51 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122826435</v>
+        <v>122825504</v>
       </c>
       <c r="B35" t="n">
-        <v>90957</v>
+        <v>79881</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4655,25 +4686,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4683,10 +4714,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529156</v>
+        <v>529093</v>
       </c>
       <c r="R35" t="n">
-        <v>6998208</v>
+        <v>6998292</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4729,6 +4760,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Sten/berg på land</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stone/rock on land</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4745,10 +4791,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122823485</v>
+        <v>122825546</v>
       </c>
       <c r="B36" t="n">
-        <v>78771</v>
+        <v>79757</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4757,46 +4803,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529041</v>
+        <v>529031</v>
       </c>
       <c r="R36" t="n">
-        <v>6998374</v>
+        <v>6998345</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4823,14 +4864,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
+          <t>På bark på stam av levande gammal asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4841,51 +4892,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122825983</v>
+        <v>122823202</v>
       </c>
       <c r="B37" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4922,13 +4948,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529112</v>
+        <v>529003</v>
       </c>
       <c r="R37" t="n">
-        <v>6998258</v>
+        <v>6998380</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4960,11 +4986,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4976,27 +4997,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5014,10 +5035,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122825639</v>
+        <v>122826011</v>
       </c>
       <c r="B38" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5030,37 +5051,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529113</v>
+        <v>529111</v>
       </c>
       <c r="R38" t="n">
-        <v>6998294</v>
+        <v>6998222</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5087,11 +5117,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gammal asp</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5100,51 +5145,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122823649</v>
+        <v>122825531</v>
       </c>
       <c r="B39" t="n">
-        <v>78771</v>
+        <v>79882</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5153,25 +5173,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5186,13 +5206,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529030</v>
+        <v>529096</v>
       </c>
       <c r="R39" t="n">
-        <v>6998340</v>
+        <v>6998283</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5224,11 +5244,6 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Långväxta fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5243,24 +5258,14 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Sten/berg på land</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Stone/rock on land</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5278,10 +5283,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122826028</v>
+        <v>122825438</v>
       </c>
       <c r="B40" t="n">
-        <v>79852</v>
+        <v>78509</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5294,21 +5299,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5318,13 +5323,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529125</v>
+        <v>529040</v>
       </c>
       <c r="R40" t="n">
-        <v>6998223</v>
+        <v>6998249</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5351,11 +5356,26 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5364,51 +5384,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122824740</v>
+        <v>122823485</v>
       </c>
       <c r="B41" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5439,19 +5434,24 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528995</v>
+        <v>529041</v>
       </c>
       <c r="R41" t="n">
-        <v>6998368</v>
+        <v>6998374</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Långväxta fertila bålar med riklig förekomst av apothecier.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
